--- a/outputs/LAA_roster_system.xlsx
+++ b/outputs/LAA_roster_system.xlsx
@@ -10250,28 +10250,28 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Jake Munroe</t>
+          <t>Liordanys Menendez</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.231</v>
+        <v>0.216</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.303</v>
+        <v>0.309</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-0.6899999999999999</v>
+        <v>3.12</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
@@ -10324,28 +10324,28 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Liordanys Menendez</t>
+          <t>Jake Munroe</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.216</v>
+        <v>0.231</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.309</v>
+        <v>0.303</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>0.093</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>3.12</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
@@ -12774,11 +12774,11 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Alexander Rincon</t>
+          <t>Carlos Castillo</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
@@ -12786,16 +12786,16 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.198</v>
+        <v>0.167</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.28</v>
+        <v>0.294</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>0.082</v>
+        <v>0.127</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1.77</v>
+        <v>2.57</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
@@ -12848,11 +12848,11 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Carlos Castillo</t>
+          <t>Alexander Rincon</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
@@ -12860,16 +12860,16 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.167</v>
+        <v>0.198</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.294</v>
+        <v>0.28</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>0.127</v>
+        <v>0.082</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>2.57</v>
+        <v>1.77</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
@@ -14068,28 +14068,28 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Jose Lavagnino</t>
+          <t>Leandro Scotti</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.143</v>
+        <v>0.115</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.265</v>
+        <v>0.285</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>0.122</v>
+        <v>0.171</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>-2.93</v>
+        <v>-1.52</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
@@ -14142,28 +14142,28 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Leandro Scotti</t>
+          <t>Jose Lavagnino</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.115</v>
+        <v>0.143</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.285</v>
+        <v>0.265</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>0.171</v>
+        <v>0.122</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>-1.52</v>
+        <v>-2.93</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>

--- a/outputs/LAA_roster_system.xlsx
+++ b/outputs/LAA_roster_system.xlsx
@@ -4013,7 +4013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4021,6 +4021,7 @@
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -4048,10 +4049,15 @@
       </c>
       <c r="D3" s="32" t="inlineStr">
         <is>
+          <t>Top level</t>
+        </is>
+      </c>
+      <c r="E3" s="32" t="inlineStr">
+        <is>
           <t>Best</t>
         </is>
       </c>
-      <c r="E3" s="32" t="inlineStr">
+      <c r="F3" s="32" t="inlineStr">
         <is>
           <t>BestP</t>
         </is>
@@ -4071,10 +4077,15 @@
           <t>RF</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="F4" s="4" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -4092,10 +4103,15 @@
           <t>RF</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>-2.1</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="F5" s="4" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -4113,10 +4129,15 @@
           <t>RF</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>-3.7</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="F6" s="4" t="n">
         <v>1.1</v>
       </c>
     </row>
@@ -4134,10 +4155,15 @@
           <t>RF</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="F7" s="4" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -4155,10 +4181,15 @@
           <t>CF</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>-4.3</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="F8" s="4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4176,10 +4207,15 @@
           <t>RF</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>-3.9</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="F9" s="4" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4197,10 +4233,15 @@
           <t>RF</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>R(DLR)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>-8.5</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="F10" s="4" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4218,10 +4259,15 @@
           <t>SS</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>-3.5</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="F11" s="4" t="n">
         <v>-1</v>
       </c>
     </row>
@@ -4239,10 +4285,15 @@
           <t>SS</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>-5.1</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="F12" s="4" t="n">
         <v>-1.3</v>
       </c>
     </row>
@@ -4260,10 +4311,15 @@
           <t>DH</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>-4.8</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="F13" s="4" t="n">
         <v>-1.3</v>
       </c>
     </row>
@@ -4281,10 +4337,15 @@
           <t>3B</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>-5.5</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="F14" s="4" t="n">
         <v>-1.5</v>
       </c>
     </row>
@@ -4302,10 +4363,15 @@
           <t>1B</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>-6.5</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="F15" s="4" t="n">
         <v>-1.6</v>
       </c>
     </row>
@@ -4323,10 +4389,15 @@
           <t>C</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>-3.7</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="F16" s="4" t="n">
         <v>-1.6</v>
       </c>
     </row>
@@ -4344,10 +4415,15 @@
           <t>RF</t>
         </is>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>R(DLR)</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>-8.199999999999999</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="F17" s="4" t="n">
         <v>-1.7</v>
       </c>
     </row>
@@ -4365,10 +4441,15 @@
           <t>RF</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>R(DLR)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>-9.199999999999999</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="F18" s="4" t="n">
         <v>-1.8</v>
       </c>
     </row>
@@ -4386,10 +4467,15 @@
           <t>SS</t>
         </is>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>-6.8</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="F19" s="4" t="n">
         <v>-1.9</v>
       </c>
     </row>
@@ -4407,10 +4493,15 @@
           <t>3B</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>-4.8</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="F20" s="4" t="n">
         <v>-2.1</v>
       </c>
     </row>
@@ -4428,10 +4519,15 @@
           <t>SS</t>
         </is>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>-6.8</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="F21" s="4" t="n">
         <v>-2.1</v>
       </c>
     </row>
@@ -4449,10 +4545,15 @@
           <t>SS</t>
         </is>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>-6.5</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="F22" s="4" t="n">
         <v>-2.1</v>
       </c>
     </row>
@@ -4470,10 +4571,15 @@
           <t>SS</t>
         </is>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n">
         <v>-4.8</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="F23" s="4" t="n">
         <v>-2.2</v>
       </c>
     </row>
@@ -4491,10 +4597,15 @@
           <t>1B</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>-4.4</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="F24" s="4" t="n">
         <v>-2.2</v>
       </c>
     </row>
@@ -4512,10 +4623,15 @@
           <t>C</t>
         </is>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n">
         <v>-5.5</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="F25" s="4" t="n">
         <v>-2.3</v>
       </c>
     </row>
@@ -4533,10 +4649,15 @@
           <t>1B</t>
         </is>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n">
         <v>-7</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="F26" s="4" t="n">
         <v>-2.5</v>
       </c>
     </row>
@@ -4554,10 +4675,15 @@
           <t>SS</t>
         </is>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>R(DLR)</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n">
         <v>-11.1</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="F27" s="4" t="n">
         <v>-2.5</v>
       </c>
     </row>
@@ -4575,10 +4701,15 @@
           <t>RF</t>
         </is>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
         <v>-5.4</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="F28" s="4" t="n">
         <v>-2.6</v>
       </c>
     </row>
@@ -4596,10 +4727,15 @@
           <t>SS</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n">
         <v>-5.1</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="F29" s="4" t="n">
         <v>-3</v>
       </c>
     </row>
@@ -4617,10 +4753,15 @@
           <t>SS</t>
         </is>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n">
         <v>-4.3</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="F30" s="4" t="n">
         <v>-3.3</v>
       </c>
     </row>
@@ -4638,10 +4779,15 @@
           <t>SS</t>
         </is>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>R(DLR)</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
         <v>-7.4</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="F31" s="4" t="n">
         <v>-3.5</v>
       </c>
     </row>
@@ -4659,10 +4805,15 @@
           <t>1B</t>
         </is>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>R(DLR)</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
         <v>-11.8</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="F32" s="4" t="n">
         <v>-3.9</v>
       </c>
     </row>
@@ -4680,10 +4831,15 @@
           <t>1B</t>
         </is>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
         <v>-7.5</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="F33" s="4" t="n">
         <v>-4.1</v>
       </c>
     </row>
@@ -4701,10 +4857,15 @@
           <t>SS</t>
         </is>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n">
         <v>-8.800000000000001</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="F34" s="4" t="n">
         <v>-4.3</v>
       </c>
     </row>
@@ -4722,10 +4883,15 @@
           <t>C</t>
         </is>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>R(DLR)</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
         <v>-11.2</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="F35" s="4" t="n">
         <v>-4.4</v>
       </c>
     </row>
@@ -4743,10 +4909,15 @@
           <t>1B</t>
         </is>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>R(DLR)</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n">
         <v>-8.9</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="F36" s="4" t="n">
         <v>-5.1</v>
       </c>
     </row>
@@ -4764,10 +4935,15 @@
           <t>2B</t>
         </is>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>R(DLR)</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="n">
         <v>-10.5</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="F37" s="4" t="n">
         <v>-5.2</v>
       </c>
     </row>
@@ -4785,10 +4961,15 @@
           <t>3B</t>
         </is>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>R(DLR)</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n">
         <v>-13.3</v>
       </c>
-      <c r="E38" s="4" t="n">
+      <c r="F38" s="4" t="n">
         <v>-6.2</v>
       </c>
     </row>
@@ -4806,10 +4987,15 @@
           <t>1B</t>
         </is>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>R(DLR)</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="n">
         <v>-12.3</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="F39" s="4" t="n">
         <v>-6.4</v>
       </c>
     </row>
@@ -4827,16 +5013,21 @@
           <t>C</t>
         </is>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="n">
         <v>-6.7</v>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="F40" s="4" t="n">
         <v>-6.4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4848,15 +5039,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -4879,20 +5071,25 @@
       </c>
       <c r="C3" s="32" t="inlineStr">
         <is>
+          <t>Top level</t>
+        </is>
+      </c>
+      <c r="D3" s="32" t="inlineStr">
+        <is>
           <t>pwOBA</t>
         </is>
       </c>
-      <c r="D3" s="32" t="inlineStr">
+      <c r="E3" s="32" t="inlineStr">
         <is>
           <t>sp_warP</t>
         </is>
       </c>
-      <c r="E3" s="32" t="inlineStr">
+      <c r="F3" s="32" t="inlineStr">
         <is>
           <t>rp_warP</t>
         </is>
       </c>
-      <c r="F3" s="32" t="inlineStr">
+      <c r="G3" s="32" t="inlineStr">
         <is>
           <t>IP</t>
         </is>
@@ -4907,14 +5104,19 @@
       <c r="B4" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
         <v>0.403</v>
       </c>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="n">
         <v>-0.6</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="G4" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4927,16 +5129,21 @@
       <c r="B5" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
         <v>0.395</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="E5" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="F5" s="4" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4949,14 +5156,19 @@
       <c r="B6" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
         <v>0.403</v>
       </c>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4969,14 +5181,19 @@
       <c r="B7" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
         <v>0.388</v>
       </c>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4989,16 +5206,21 @@
       <c r="B8" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="E8" s="4" t="n">
         <v>-2.4</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="F8" s="4" t="n">
         <v>-0.8</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5011,14 +5233,19 @@
       <c r="B9" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>0.403</v>
       </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5031,16 +5258,21 @@
       <c r="B10" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>0.401</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="E10" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="F10" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5053,16 +5285,21 @@
       <c r="B11" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
         <v>0.396</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="E11" s="4" t="n">
         <v>-3.4</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="F11" s="4" t="n">
         <v>-1.1</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5075,16 +5312,21 @@
       <c r="B12" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
         <v>0.402</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="E12" s="4" t="n">
         <v>-3.3</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="F12" s="4" t="n">
         <v>-1.1</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5097,16 +5339,21 @@
       <c r="B13" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
         <v>0.403</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="E13" s="4" t="n">
         <v>-3.6</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="F13" s="4" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5119,16 +5366,21 @@
       <c r="B14" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="E14" s="4" t="n">
         <v>-3.5</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="F14" s="4" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5141,16 +5393,21 @@
       <c r="B15" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
         <v>0.402</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="E15" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="F15" s="4" t="n">
         <v>-1.3</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5163,14 +5420,19 @@
       <c r="B16" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
         <v>0.396</v>
       </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5183,16 +5445,21 @@
       <c r="B17" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
         <v>0.395</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="E17" s="4" t="n">
         <v>-4.2</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="F17" s="4" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5205,14 +5472,19 @@
       <c r="B18" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5225,22 +5497,27 @@
       <c r="B19" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="E19" s="4" t="n">
         <v>-4.2</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="F19" s="4" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/LAA_roster_system.xlsx
+++ b/outputs/LAA_roster_system.xlsx
@@ -1257,20 +1257,20 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Chase Silseth</t>
+          <t>Tyler Samaniego</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.349</v>
+        <v>0.354</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.35</v>
+        <v>0.348</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.7</v>
+        <v>-0.6</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>0</v>
@@ -1289,27 +1289,27 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Jose Fermin</t>
+          <t>Yerry Rodriguez</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.356</v>
+        <v>0.353</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.317</v>
+        <v>0.367</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Mid leverage</t>
+          <t>Low leverage / depth</t>
         </is>
       </c>
     </row>
@@ -1321,20 +1321,20 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Tyler Samaniego</t>
+          <t>Tyler Owens</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.354</v>
+        <v>0.362</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.348</v>
+        <v>0.325</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>0</v>
@@ -1353,23 +1353,23 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Yerry Rodriguez</t>
+          <t>Ryan Zeferjahn</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>29</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.353</v>
+        <v>0.359</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.367</v>
+        <v>0.358</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
@@ -1385,20 +1385,20 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Tyler Owens</t>
+          <t>Will Gervase</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.362</v>
+        <v>0.366</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.325</v>
+        <v>0.337</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>0</v>
@@ -1417,20 +1417,20 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Ryan Zeferjahn</t>
+          <t>Carlos Espinosa</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.359</v>
+        <v>0.38</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.358</v>
+        <v>0.322</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.9</v>
+        <v>-0.1</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>0</v>
@@ -1449,27 +1449,27 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Will Gervase</t>
+          <t>Bridger Holmes</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
         <v>24</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.366</v>
+        <v>0.382</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.337</v>
+        <v>0.32</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.4</v>
+        <v>-0</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Low leverage / depth</t>
+          <t>Mid leverage</t>
         </is>
       </c>
     </row>
@@ -1479,26 +1479,36 @@
           <t>RP8</t>
         </is>
       </c>
-      <c r="B18" s="29" t="inlineStr">
-        <is>
-          <t>-- empty --</t>
-        </is>
-      </c>
-      <c r="C18" s="30" t="n"/>
-      <c r="D18" s="30" t="n"/>
-      <c r="E18" s="30" t="n"/>
-      <c r="F18" s="30" t="n"/>
-      <c r="G18" s="30" t="n"/>
-      <c r="H18" s="31" t="inlineStr">
-        <is>
-          <t>Sign FA</t>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Lucas Mahlstedt</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Low leverage / depth</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Total: 12 pitchers (target 13)</t>
+          <t>Total: 13 pitchers (target 13)</t>
         </is>
       </c>
     </row>
@@ -1794,20 +1804,20 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Carlos Espinosa</t>
+          <t>Pedro Da Costa Lemos</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.38</v>
+        <v>0.386</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.322</v>
+        <v>0.34</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.1</v>
+        <v>-0.5</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
@@ -1826,27 +1836,27 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Bridger Holmes</t>
+          <t>Sam Tookoian</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.382</v>
+        <v>0.389</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.32</v>
+        <v>0.346</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0</v>
+        <v>-0.6</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Mid leverage</t>
+          <t>Low leverage / depth</t>
         </is>
       </c>
     </row>
@@ -1858,20 +1868,20 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Lucas Mahlstedt</t>
+          <t>Samy Natera Jr.</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.384</v>
+        <v>0.379</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.323</v>
+        <v>0.372</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.1</v>
+        <v>-1.2</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>0</v>
@@ -1890,20 +1900,20 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Samy Natera Jr.</t>
+          <t>Fulton Lockhart</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.379</v>
+        <v>0.393</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.372</v>
+        <v>0.345</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>0</v>
@@ -1920,19 +1930,29 @@
           <t>RP6</t>
         </is>
       </c>
-      <c r="B16" s="29" t="inlineStr">
-        <is>
-          <t>-- empty --</t>
-        </is>
-      </c>
-      <c r="C16" s="30" t="n"/>
-      <c r="D16" s="30" t="n"/>
-      <c r="E16" s="30" t="n"/>
-      <c r="F16" s="30" t="n"/>
-      <c r="G16" s="30" t="n"/>
-      <c r="H16" s="31" t="inlineStr">
-        <is>
-          <t>Sign FA</t>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Yeferson Vargas</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Low leverage / depth</t>
         </is>
       </c>
     </row>
@@ -1942,19 +1962,29 @@
           <t>RP7</t>
         </is>
       </c>
-      <c r="B17" s="29" t="inlineStr">
-        <is>
-          <t>-- empty --</t>
-        </is>
-      </c>
-      <c r="C17" s="30" t="n"/>
-      <c r="D17" s="30" t="n"/>
-      <c r="E17" s="30" t="n"/>
-      <c r="F17" s="30" t="n"/>
-      <c r="G17" s="30" t="n"/>
-      <c r="H17" s="31" t="inlineStr">
-        <is>
-          <t>Sign FA</t>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Owen Wild</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Low leverage / depth</t>
         </is>
       </c>
     </row>
@@ -1964,26 +1994,36 @@
           <t>RP8</t>
         </is>
       </c>
-      <c r="B18" s="29" t="inlineStr">
-        <is>
-          <t>-- empty --</t>
-        </is>
-      </c>
-      <c r="C18" s="30" t="n"/>
-      <c r="D18" s="30" t="n"/>
-      <c r="E18" s="30" t="n"/>
-      <c r="F18" s="30" t="n"/>
-      <c r="G18" s="30" t="n"/>
-      <c r="H18" s="31" t="inlineStr">
-        <is>
-          <t>Sign FA</t>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Peyton Olejnik</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Low leverage / depth</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Total: 10 pitchers (target 13)</t>
+          <t>Total: 13 pitchers (target 13)</t>
         </is>
       </c>
     </row>
@@ -2247,20 +2287,20 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Pedro Da Costa Lemos</t>
+          <t>Christopher Hernandez</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.386</v>
+        <v>0.395</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.34</v>
+        <v>0.337</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>0</v>
@@ -2279,20 +2319,20 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Sam Tookoian</t>
+          <t>Jhon Almonte</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.389</v>
+        <v>0.403</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.346</v>
+        <v>0.357</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
@@ -2311,20 +2351,20 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Fulton Lockhart</t>
+          <t>Luke Schmolke</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
         <v>23</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.393</v>
+        <v>0.395</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.345</v>
+        <v>0.354</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.6</v>
+        <v>-0.8</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>0</v>
@@ -2343,20 +2383,20 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Yeferson Vargas</t>
+          <t>Tate McKee</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>22</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.394</v>
+        <v>0.403</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.354</v>
+        <v>0.34</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>0</v>
@@ -2375,17 +2415,17 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Owen Wild</t>
+          <t>Keythel Key</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.385</v>
+        <v>0.396</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>-0.8</v>
@@ -2407,20 +2447,20 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Peyton Olejnik</t>
+          <t>Fabian Soto</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.389</v>
+        <v>0.4</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.35</v>
+        <v>0.368</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.7</v>
+        <v>-1.1</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>0</v>
@@ -2762,20 +2802,20 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Christopher Hernandez</t>
+          <t>Miguel Liendo</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.395</v>
+        <v>0.4</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.337</v>
+        <v>0.36</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.4</v>
+        <v>-0.9</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>0</v>
@@ -2826,20 +2866,20 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Jhon Almonte</t>
+          <t>Cole Raymond</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
         <v>20</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.403</v>
+        <v>0.401</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.357</v>
+        <v>0.369</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>0</v>
@@ -2858,20 +2898,20 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Luke Schmolke</t>
+          <t>Jhostin Betances</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.395</v>
+        <v>0.4</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.354</v>
+        <v>0.373</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.8</v>
+        <v>-1.2</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>0</v>
@@ -2890,20 +2930,20 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Tate McKee</t>
+          <t>Barrett Kent</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
         <v>22</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.403</v>
+        <v>0.397</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.34</v>
+        <v>0.365</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>0</v>
@@ -2922,20 +2962,20 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Keythel Key</t>
+          <t>Dioris De La Rosa</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.396</v>
+        <v>0.4</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.355</v>
+        <v>0.378</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.8</v>
+        <v>-1.3</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>0</v>
@@ -2954,7 +2994,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Fabian Soto</t>
+          <t>Fabian Gallardo</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
@@ -2964,10 +3004,10 @@
         <v>0.4</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.368</v>
+        <v>0.378</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.1</v>
+        <v>-1.3</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>0</v>
@@ -2986,20 +3026,20 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Cole Raymond</t>
+          <t>Jostin Alcantara</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
         <v>20</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.401</v>
+        <v>0.399</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.369</v>
+        <v>0.394</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.1</v>
+        <v>-1.6</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>0</v>
@@ -3277,7 +3317,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Miguel Liendo</t>
+          <t>Freddy Hernandez</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
@@ -3287,10 +3327,10 @@
         <v>0.4</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.36</v>
+        <v>0.374</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.9</v>
+        <v>-1.2</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>0</v>
@@ -3309,20 +3349,20 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Freddy Hernandez</t>
+          <t>Juan Jordan</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
         <v>19</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.4</v>
+        <v>0.402</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.374</v>
+        <v>0.377</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.2</v>
+        <v>-1.3</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
@@ -3341,17 +3381,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Juan Jordan</t>
+          <t>Sebastian Caseres</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
         <v>19</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.402</v>
+        <v>0.401</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.377</v>
+        <v>0.381</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>-1.3</v>
@@ -3373,20 +3413,20 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Jhostin Betances</t>
+          <t>Anllelo Gutierrez</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.4</v>
+        <v>0.403</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.373</v>
+        <v>0.381</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.2</v>
+        <v>-1.3</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>0</v>
@@ -3405,20 +3445,20 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Sebastian Caseres</t>
+          <t>Wilner Berroteran</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
         <v>19</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.401</v>
+        <v>0.4</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.381</v>
+        <v>0.383</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>0</v>
@@ -3437,20 +3477,20 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Barrett Kent</t>
+          <t>Anderson Encarnacion</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.397</v>
+        <v>0.402</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.365</v>
+        <v>0.386</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1</v>
+        <v>-1.4</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>0</v>
@@ -3469,7 +3509,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Wilner Berroteran</t>
+          <t>Felix Tapia</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
@@ -3479,10 +3519,10 @@
         <v>0.4</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.383</v>
+        <v>0.396</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.4</v>
+        <v>-1.7</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>0</v>
@@ -3501,20 +3541,20 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Dioris De La Rosa</t>
+          <t>Steuri Amancio</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.4</v>
+        <v>0.402</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.378</v>
+        <v>0.396</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.3</v>
+        <v>-1.7</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>0</v>
@@ -3790,29 +3830,19 @@
           <t>RP1</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Anllelo Gutierrez</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>0.403</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>Low leverage / depth</t>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>-- empty --</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="30" t="n"/>
+      <c r="E11" s="30" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
+      <c r="H11" s="31" t="inlineStr">
+        <is>
+          <t>Sign FA</t>
         </is>
       </c>
     </row>
@@ -3822,29 +3852,19 @@
           <t>RP2</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Fabian Gallardo</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0.378</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>Low leverage / depth</t>
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>-- empty --</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="n"/>
+      <c r="D12" s="30" t="n"/>
+      <c r="E12" s="30" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
+      <c r="H12" s="31" t="inlineStr">
+        <is>
+          <t>Sign FA</t>
         </is>
       </c>
     </row>
@@ -3854,29 +3874,19 @@
           <t>RP3</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Anderson Encarnacion</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>0.386</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>Low leverage / depth</t>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>-- empty --</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="n"/>
+      <c r="D13" s="30" t="n"/>
+      <c r="E13" s="30" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
+      <c r="H13" s="31" t="inlineStr">
+        <is>
+          <t>Sign FA</t>
         </is>
       </c>
     </row>
@@ -3886,29 +3896,19 @@
           <t>RP4</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Jostin Alcantara</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>0.399</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>0.394</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Low leverage / depth</t>
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>-- empty --</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="n"/>
+      <c r="D14" s="30" t="n"/>
+      <c r="E14" s="30" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="30" t="n"/>
+      <c r="H14" s="31" t="inlineStr">
+        <is>
+          <t>Sign FA</t>
         </is>
       </c>
     </row>
@@ -3918,29 +3918,19 @@
           <t>RP5</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Felix Tapia</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>Low leverage / depth</t>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>-- empty --</t>
+        </is>
+      </c>
+      <c r="C15" s="30" t="n"/>
+      <c r="D15" s="30" t="n"/>
+      <c r="E15" s="30" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
+      <c r="H15" s="31" t="inlineStr">
+        <is>
+          <t>Sign FA</t>
         </is>
       </c>
     </row>
@@ -3950,29 +3940,19 @@
           <t>RP6</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Steuri Amancio</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Low leverage / depth</t>
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>-- empty --</t>
+        </is>
+      </c>
+      <c r="C16" s="30" t="n"/>
+      <c r="D16" s="30" t="n"/>
+      <c r="E16" s="30" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="30" t="n"/>
+      <c r="H16" s="31" t="inlineStr">
+        <is>
+          <t>Sign FA</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4003,7 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Total: 11 pitchers (target 13)</t>
+          <t>Total: 5 pitchers (target 13)</t>
         </is>
       </c>
     </row>
@@ -15205,19 +15185,29 @@
           <t>RP7</t>
         </is>
       </c>
-      <c r="B17" s="29" t="inlineStr">
-        <is>
-          <t>-- empty --</t>
-        </is>
-      </c>
-      <c r="C17" s="30" t="n"/>
-      <c r="D17" s="30" t="n"/>
-      <c r="E17" s="30" t="n"/>
-      <c r="F17" s="30" t="n"/>
-      <c r="G17" s="30" t="n"/>
-      <c r="H17" s="31" t="inlineStr">
-        <is>
-          <t>Sign FA</t>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Chase Silseth</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Low leverage / depth</t>
         </is>
       </c>
     </row>
@@ -15227,26 +15217,36 @@
           <t>RP8</t>
         </is>
       </c>
-      <c r="B18" s="29" t="inlineStr">
-        <is>
-          <t>-- empty --</t>
-        </is>
-      </c>
-      <c r="C18" s="30" t="n"/>
-      <c r="D18" s="30" t="n"/>
-      <c r="E18" s="30" t="n"/>
-      <c r="F18" s="30" t="n"/>
-      <c r="G18" s="30" t="n"/>
-      <c r="H18" s="31" t="inlineStr">
-        <is>
-          <t>Sign FA</t>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Jose Fermin</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Mid leverage</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Total: 11 pitchers (target 13)</t>
+          <t>Total: 13 pitchers (target 13)</t>
         </is>
       </c>
     </row>

--- a/outputs/LAA_roster_system.xlsx
+++ b/outputs/LAA_roster_system.xlsx
@@ -1090,20 +1090,20 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Brody Hopkins</t>
+          <t>Liam Peterson</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.339</v>
+        <v>0.369</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.309</v>
+        <v>0.3</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>0</v>
@@ -1122,27 +1122,27 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Victor Mederos</t>
+          <t>Brody Hopkins</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
         <v>25</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.354</v>
+        <v>0.339</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.331</v>
+        <v>0.309</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Innings eater</t>
+          <t>Mid-rotation</t>
         </is>
       </c>
     </row>
@@ -1154,23 +1154,23 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Braxton Bragg</t>
+          <t>Victor Mederos</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.356</v>
+        <v>0.354</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.33</v>
+        <v>0.331</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
@@ -1186,23 +1186,23 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Caden Dana</t>
+          <t>Braxton Bragg</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.364</v>
+        <v>0.356</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.336</v>
+        <v>0.33</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.1</v>
+        <v>-0.7</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -1218,20 +1218,20 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Joel Hurtado</t>
+          <t>Caden Dana</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.366</v>
+        <v>0.364</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.328</v>
+        <v>0.336</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.6</v>
+        <v>-1.1</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>0</v>
@@ -1605,27 +1605,27 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Liam Peterson</t>
+          <t>Franklin Gomez</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
         <v>21</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.369</v>
+        <v>0.376</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.3</v>
+        <v>0.335</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Mid-rotation</t>
+          <t>Innings eater</t>
         </is>
       </c>
     </row>
@@ -1637,27 +1637,27 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Franklin Gomez</t>
+          <t>Tyler Bremner</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.376</v>
+        <v>0.375</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.335</v>
+        <v>0.318</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.1</v>
+        <v>0.1</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Innings eater</t>
+          <t>Back-end starter</t>
         </is>
       </c>
     </row>
@@ -1669,27 +1669,27 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Tyler Bremner</t>
+          <t>Joel Hurtado</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.375</v>
+        <v>0.366</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.318</v>
+        <v>0.328</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Back-end starter</t>
+          <t>Innings eater</t>
         </is>
       </c>
     </row>
@@ -2319,20 +2319,20 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Jhon Almonte</t>
+          <t>Miguel Liendo</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.403</v>
+        <v>0.4</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.357</v>
+        <v>0.36</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
@@ -2351,17 +2351,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Luke Schmolke</t>
+          <t>Jhon Almonte</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.395</v>
+        <v>0.403</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.354</v>
+        <v>0.357</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>-0.8</v>
@@ -2383,20 +2383,20 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Tate McKee</t>
+          <t>Freddy Hernandez</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.403</v>
+        <v>0.4</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.34</v>
+        <v>0.374</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.5</v>
+        <v>-1.2</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>0</v>
@@ -2415,17 +2415,17 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Keythel Key</t>
+          <t>Luke Schmolke</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
         <v>23</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.396</v>
+        <v>0.395</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.355</v>
+        <v>0.354</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>-0.8</v>
@@ -2447,20 +2447,20 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Fabian Soto</t>
+          <t>Tate McKee</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.4</v>
+        <v>0.403</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.368</v>
+        <v>0.34</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.1</v>
+        <v>-0.5</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>0</v>
@@ -2635,27 +2635,27 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Xavier Mitchell</t>
+          <t>Ruben Gonzalez</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.401</v>
+        <v>0.403</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.324</v>
+        <v>0.302</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>-0.3</v>
+        <v>1.1</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Innings eater</t>
+          <t>Mid-rotation</t>
         </is>
       </c>
     </row>
@@ -2667,27 +2667,27 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Kai Fyke</t>
+          <t>Kendri Fana</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.402</v>
+        <v>0.401</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.325</v>
+        <v>0.307</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.4</v>
+        <v>0.8</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Innings eater</t>
+          <t>Mid-rotation</t>
         </is>
       </c>
     </row>
@@ -2699,27 +2699,27 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Talon Haley</t>
+          <t>Trey Rangel</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.401</v>
+        <v>0.399</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.332</v>
+        <v>0.317</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.9</v>
+        <v>0.1</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Innings eater</t>
+          <t>Back-end starter</t>
         </is>
       </c>
     </row>
@@ -2731,17 +2731,17 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>CJ Gray</t>
+          <t>Danny Balderama</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.402</v>
+        <v>0.403</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.332</v>
+        <v>0.33</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>-0.8</v>
@@ -2763,20 +2763,20 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Dylan Jordan</t>
+          <t>Xavier Mitchell</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.398</v>
+        <v>0.401</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.343</v>
+        <v>0.324</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.5</v>
+        <v>-0.3</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>0</v>
@@ -2802,20 +2802,20 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Miguel Liendo</t>
+          <t>Drew Lafferty</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.4</v>
+        <v>0.401</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.36</v>
+        <v>0.328</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.9</v>
+        <v>-0.2</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>0</v>
@@ -2834,20 +2834,20 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Drew Lafferty</t>
+          <t>Keythel Key</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
         <v>23</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.401</v>
+        <v>0.396</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.328</v>
+        <v>0.355</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.2</v>
+        <v>-0.8</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
@@ -2866,17 +2866,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Cole Raymond</t>
+          <t>Fabian Soto</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.401</v>
+        <v>0.4</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>-1.1</v>
@@ -2898,20 +2898,20 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Jhostin Betances</t>
+          <t>Juan Jordan</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.4</v>
+        <v>0.402</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.373</v>
+        <v>0.377</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.2</v>
+        <v>-1.3</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>0</v>
@@ -2930,20 +2930,20 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Barrett Kent</t>
+          <t>Cole Raymond</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.397</v>
+        <v>0.401</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.365</v>
+        <v>0.369</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>0</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Dioris De La Rosa</t>
+          <t>Jhostin Betances</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
@@ -2972,10 +2972,10 @@
         <v>0.4</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.378</v>
+        <v>0.373</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>0</v>
@@ -2994,17 +2994,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Fabian Gallardo</t>
+          <t>Sebastian Caseres</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.4</v>
+        <v>0.401</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.378</v>
+        <v>0.381</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>-1.3</v>
@@ -3026,20 +3026,20 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Jostin Alcantara</t>
+          <t>Anllelo Gutierrez</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.399</v>
+        <v>0.403</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.394</v>
+        <v>0.381</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.6</v>
+        <v>-1.3</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>0</v>
@@ -3150,27 +3150,27 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Kendri Fana</t>
+          <t>Kai Fyke</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.401</v>
+        <v>0.402</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.307</v>
+        <v>0.325</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.8</v>
+        <v>-0.4</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Mid-rotation</t>
+          <t>Innings eater</t>
         </is>
       </c>
     </row>
@@ -3182,27 +3182,27 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Trey Rangel</t>
+          <t>Kaiden McCarthy</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.399</v>
+        <v>0.402</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.317</v>
+        <v>0.349</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1</v>
+        <v>-1.9</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Back-end starter</t>
+          <t>Innings eater</t>
         </is>
       </c>
     </row>
@@ -3214,20 +3214,20 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Kaiden McCarthy</t>
+          <t>Talon Haley</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.402</v>
+        <v>0.401</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.349</v>
+        <v>0.332</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.9</v>
+        <v>-0.9</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>0</v>
@@ -3246,20 +3246,20 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Ubaldo Soto</t>
+          <t>CJ Gray</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>20</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.4</v>
+        <v>0.402</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.347</v>
+        <v>0.332</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1.8</v>
+        <v>-0.8</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>0</v>
@@ -3278,20 +3278,20 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Alexander Garcia</t>
+          <t>Dylan Jordan</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.4</v>
+        <v>0.398</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.365</v>
+        <v>0.343</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-3</v>
+        <v>-1.5</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>0</v>
@@ -3317,20 +3317,20 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Freddy Hernandez</t>
+          <t>Barrett Kent</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.4</v>
+        <v>0.397</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.374</v>
+        <v>0.365</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.2</v>
+        <v>-1</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>0</v>
@@ -3349,20 +3349,20 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Juan Jordan</t>
+          <t>Wilner Berroteran</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
         <v>19</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.402</v>
+        <v>0.4</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.377</v>
+        <v>0.383</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
@@ -3381,17 +3381,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Sebastian Caseres</t>
+          <t>Fabian Gallardo</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.401</v>
+        <v>0.4</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.381</v>
+        <v>0.378</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>-1.3</v>
@@ -3413,17 +3413,17 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Anllelo Gutierrez</t>
+          <t>Dioris De La Rosa</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.403</v>
+        <v>0.4</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.381</v>
+        <v>0.378</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>-1.3</v>
@@ -3445,17 +3445,17 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Wilner Berroteran</t>
+          <t>Anderson Encarnacion</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.4</v>
+        <v>0.402</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.383</v>
+        <v>0.386</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>-1.4</v>
@@ -3477,20 +3477,20 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Anderson Encarnacion</t>
+          <t>Jostin Alcantara</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.402</v>
+        <v>0.399</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.386</v>
+        <v>0.394</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.4</v>
+        <v>-1.6</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>0</v>
@@ -3665,27 +3665,27 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Ruben Gonzalez</t>
+          <t>Ubaldo Soto</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.403</v>
+        <v>0.4</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.302</v>
+        <v>0.347</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1.1</v>
+        <v>-1.8</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Mid-rotation</t>
+          <t>Innings eater</t>
         </is>
       </c>
     </row>
@@ -3697,20 +3697,20 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Danny Balderama</t>
+          <t>Elias Ledesma</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
         <v>17</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.403</v>
+        <v>0.402</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.33</v>
+        <v>0.364</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.8</v>
+        <v>-2.9</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0</v>
@@ -3729,20 +3729,20 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Elias Ledesma</t>
+          <t>Alexander Garcia</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.402</v>
+        <v>0.4</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.364</v>
+        <v>0.365</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-2.9</v>
+        <v>-3</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>0</v>

--- a/outputs/LAA_roster_system.xlsx
+++ b/outputs/LAA_roster_system.xlsx
@@ -762,7 +762,7 @@
         <v>17</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-1.24</v>
+        <v>-1.82</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.16</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="7">
@@ -797,7 +797,7 @@
         <v>-2.54</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="8">
@@ -810,7 +810,7 @@
         <v>13</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.88</v>
+        <v>-3.92</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.15</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="9">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-5.33</v>
+        <v>-5.53</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.02</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="10">
@@ -858,7 +858,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
@@ -866,10 +866,10 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-8.83</v>
+        <v>-9.73</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-1.09</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="11">
@@ -882,7 +882,7 @@
         <v>42</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-6.79</v>
+        <v>-6.14</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.38</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="14">
@@ -2351,20 +2351,20 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Jhon Almonte</t>
+          <t>Ubaldo Soto</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
         <v>20</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.403</v>
+        <v>0.4</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.357</v>
+        <v>0.347</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.8</v>
+        <v>-0.6</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>0</v>
@@ -2834,20 +2834,20 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Keythel Key</t>
+          <t>Fabian Soto</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.396</v>
+        <v>0.4</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.355</v>
+        <v>0.368</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.8</v>
+        <v>-1.1</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
@@ -2866,20 +2866,20 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Fabian Soto</t>
+          <t>Juan Jordan</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.4</v>
+        <v>0.402</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.368</v>
+        <v>0.377</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.1</v>
+        <v>-1.3</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>0</v>
@@ -2898,20 +2898,20 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Juan Jordan</t>
+          <t>Cole Raymond</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.402</v>
+        <v>0.401</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.377</v>
+        <v>0.369</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.3</v>
+        <v>-1.1</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>0</v>
@@ -2930,20 +2930,20 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Cole Raymond</t>
+          <t>Jhostin Betances</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
         <v>20</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.401</v>
+        <v>0.4</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.369</v>
+        <v>0.373</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>0</v>
@@ -2962,20 +2962,20 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Jhostin Betances</t>
+          <t>Sebastian Caseres</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.4</v>
+        <v>0.401</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.373</v>
+        <v>0.381</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.2</v>
+        <v>-1.3</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>0</v>
@@ -2994,14 +2994,14 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Sebastian Caseres</t>
+          <t>Anllelo Gutierrez</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.401</v>
+        <v>0.403</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>0.381</v>
@@ -3026,20 +3026,20 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Anllelo Gutierrez</t>
+          <t>Barrett Kent</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.403</v>
+        <v>0.397</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.381</v>
+        <v>0.365</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>0</v>
@@ -3317,20 +3317,20 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Barrett Kent</t>
+          <t>Wilner Berroteran</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.397</v>
+        <v>0.4</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.365</v>
+        <v>0.383</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1</v>
+        <v>-1.4</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>0</v>
@@ -3349,20 +3349,20 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Wilner Berroteran</t>
+          <t>Dioris De La Rosa</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>0.4</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.383</v>
+        <v>0.378</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
@@ -3413,20 +3413,20 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Dioris De La Rosa</t>
+          <t>Anderson Encarnacion</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.4</v>
+        <v>0.402</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.378</v>
+        <v>0.386</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>0</v>
@@ -3445,20 +3445,20 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Anderson Encarnacion</t>
+          <t>Jostin Alcantara</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.402</v>
+        <v>0.399</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.386</v>
+        <v>0.394</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.4</v>
+        <v>-1.6</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>0</v>
@@ -3477,20 +3477,20 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Jostin Alcantara</t>
+          <t>Felix Tapia</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.399</v>
+        <v>0.4</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.394</v>
+        <v>0.396</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.6</v>
+        <v>-1.7</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>0</v>
@@ -3509,14 +3509,14 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Felix Tapia</t>
+          <t>Steuri Amancio</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.4</v>
+        <v>0.402</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>0.396</v>
@@ -3539,36 +3539,26 @@
           <t>RP8</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Steuri Amancio</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>0.402</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Low leverage / depth</t>
+      <c r="B18" s="29" t="inlineStr">
+        <is>
+          <t>-- empty --</t>
+        </is>
+      </c>
+      <c r="C18" s="30" t="n"/>
+      <c r="D18" s="30" t="n"/>
+      <c r="E18" s="30" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n"/>
+      <c r="H18" s="31" t="inlineStr">
+        <is>
+          <t>Sign FA</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Total: 13 pitchers (target 13)</t>
+          <t>Total: 12 pitchers (target 13)</t>
         </is>
       </c>
     </row>
@@ -3665,20 +3655,20 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Ubaldo Soto</t>
+          <t>Elias Ledesma</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.4</v>
+        <v>0.402</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.347</v>
+        <v>0.364</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>-1.8</v>
+        <v>-2.9</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>0</v>
@@ -3697,20 +3687,20 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Elias Ledesma</t>
+          <t>Alexander Garcia</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.402</v>
+        <v>0.4</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.364</v>
+        <v>0.365</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-2.9</v>
+        <v>-3</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0</v>
@@ -3729,20 +3719,20 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Alexander Garcia</t>
+          <t>Johnny Slawinski</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.4</v>
+        <v>0.399</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.365</v>
+        <v>0.354</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-3</v>
+        <v>-2.3</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>0</v>
@@ -3761,20 +3751,20 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Johnny Slawinski</t>
+          <t>Luke LaCourse</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>20</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.399</v>
+        <v>0.402</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.354</v>
+        <v>0.351</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>0</v>
@@ -3793,20 +3783,20 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Luke LaCourse</t>
+          <t>Jhon Almonte</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
         <v>20</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.402</v>
+        <v>0.403</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.351</v>
+        <v>0.357</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-2.1</v>
+        <v>-2.5</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>0</v>
@@ -4128,11 +4118,11 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Blake Cyr</t>
+          <t>Arol Vera</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -4141,14 +4131,14 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-3.7</v>
+        <v>-0.5</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="7">
@@ -4180,63 +4170,63 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Alec Gomez</t>
+          <t>Anthony Scull</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.1</v>
+        <v>-0.3</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>John Wimmer</t>
+          <t>Alec Gomez</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-4.2</v>
+        <v>-2.1</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Brody Hopkins</t>
+          <t>Randy De Jesus</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -4245,46 +4235,46 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.9</v>
+        <v>-1.7</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Adrian Feliz</t>
+          <t>John Wimmer</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>R(DLR)</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-8.5</v>
+        <v>-4.2</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Harold Coll</t>
+          <t>Brody Hopkins</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
@@ -4292,33 +4282,33 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.3</v>
+        <v>-3.9</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Jonny McGill</t>
+          <t>Harold Coll</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -4327,42 +4317,42 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-4.8</v>
+        <v>-3.3</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.2</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Nick Rodriguez</t>
+          <t>Edwardo Espinal</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.1</v>
+        <v>-3.4</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.3</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Ryland Zaborowski</t>
+          <t>Jonny McGill</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
@@ -4370,7 +4360,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -4379,68 +4369,68 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-5.4</v>
+        <v>-4.8</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.5</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Adonanfer Reyes</t>
+          <t>Nick Rodriguez</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>R(DLR)</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-8.199999999999999</v>
+        <v>-5.1</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.6</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Omar Martinez</t>
+          <t>Anyelo Marquez</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-4.1</v>
+        <v>-3.5</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.7</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Slate Alford</t>
+          <t>Ryland Zaborowski</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
@@ -4448,7 +4438,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -4457,76 +4447,76 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.8</v>
+        <v>-5.4</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.8</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Cole Fontenelle</t>
+          <t>Adonanfer Reyes</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>R(DLR)</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-4.8</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.9</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Samuel Capellan</t>
+          <t>Omar Martinez</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-6.8</v>
+        <v>-4.1</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.9</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Alberto Rios</t>
+          <t>Slate Alford</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -4535,46 +4525,46 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-5.5</v>
+        <v>-4.8</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-2</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Ray Garrett</t>
+          <t>Cole Fontenelle</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-6.5</v>
+        <v>-4.8</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.1</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Ashten Wong</t>
+          <t>Samuel Capellan</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
@@ -4583,28 +4573,28 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-7.2</v>
+        <v>-6.8</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.1</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Kyle West</t>
+          <t>Alberto Rios</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -4613,72 +4603,72 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-4.4</v>
+        <v>-5.5</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Will Hodo</t>
+          <t>Ray Garrett</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-6</v>
+        <v>-6.5</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Josue Demey</t>
+          <t>Ashten Wong</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>R(DLR)</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-9.9</v>
+        <v>-7.2</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-2.4</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Zack Stewart</t>
+          <t>Will Hodo</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
@@ -4687,37 +4677,37 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-2.5</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Luis Bruno</t>
+          <t>Zack Stewart</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>R(DLR)</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-11.6</v>
+        <v>-7</v>
       </c>
       <c r="F28" s="4" t="n">
         <v>-2.5</v>
@@ -4726,7 +4716,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Jose Santana</t>
+          <t>Luis Bruno</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
@@ -4734,29 +4724,29 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>R(DLR)</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-5.4</v>
+        <v>-11.6</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-2.6</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Alver Medina</t>
+          <t>Byron Castillo</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
@@ -4765,50 +4755,50 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>R(DLR)</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-7.9</v>
+        <v>-6.9</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-2.9</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Luis Rodriguez</t>
+          <t>Alver Medina</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>R(DLR)</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-4.7</v>
+        <v>-7.9</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-3</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Kevin Bruggeman</t>
+          <t>Luis Rodriguez</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
@@ -4817,46 +4807,46 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-4.3</v>
+        <v>-4.7</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-3.3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Jesus Aguilar</t>
+          <t>Victor Rodriguez</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>R(DLR)</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-13.3</v>
+        <v>-5.1</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-3.4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Robin Fernandez</t>
+          <t>Kevin Bruggeman</t>
         </is>
       </c>
       <c r="B34" s="4" t="n">
@@ -4869,28 +4859,28 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>R(DLR)</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-7.4</v>
+        <v>-4.3</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-3.5</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Mike Escolero</t>
+          <t>Jesus Aguilar</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -4899,24 +4889,24 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-11.7</v>
+        <v>-13.3</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-3.9</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Diego Rondon</t>
+          <t>Robin Fernandez</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -4925,20 +4915,20 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>-11.2</v>
+        <v>-7.4</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>-4.4</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Kason Siguenza</t>
+          <t>Mike Escolero</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
@@ -4951,50 +4941,50 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>-8.9</v>
+        <v>-11.7</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>-4.5</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Bryan Martinez</t>
+          <t>Diego Rondon</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>R(DLR)</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>-7.3</v>
+        <v>-11.2</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>-4.5</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Diego Felix</t>
+          <t>Bryan Martinez</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -5003,50 +4993,50 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>-8.699999999999999</v>
+        <v>-7.3</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>-4.8</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Salvatore Cruz</t>
+          <t>Diego Felix</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>R(DLR)</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>-12.6</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>-5.1</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>David Manzueta</t>
+          <t>Salvatore Cruz</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -5055,36 +5045,36 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>-10.5</v>
+        <v>-12.6</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>-5.2</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Sandy Ruiz</t>
+          <t>David Manzueta</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>R(DLR)</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>-7.6</v>
+        <v>-10.5</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>-5.3</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="43">
@@ -5179,7 +5169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5315,7 +5305,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Victor Garcia</t>
+          <t>Keythel Key</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
@@ -5327,11 +5317,13 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
+        <v>0.396</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>-2.3</v>
+      </c>
       <c r="F7" s="4" t="n">
-        <v>-0.9</v>
+        <v>-0.8</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>0</v>
@@ -5340,23 +5332,23 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Najer Victor</t>
+          <t>Victor Garcia</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.395</v>
+        <v>0.4</v>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="n">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>0</v>
@@ -5365,23 +5357,21 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Tyler Wood</t>
+          <t>Najer Victor</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.401</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>-3</v>
-      </c>
+        <v>0.395</v>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
       <c r="F9" s="4" t="n">
         <v>-1</v>
       </c>
@@ -5392,11 +5382,11 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Heath Andrews</t>
+          <t>Tyler Wood</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -5407,7 +5397,7 @@
         <v>0.401</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.9</v>
+        <v>-3</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>-1</v>
@@ -5419,11 +5409,11 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Brian Strange</t>
+          <t>Heath Andrews</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -5431,13 +5421,13 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.396</v>
+        <v>0.401</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-3.4</v>
+        <v>-2.9</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.1</v>
+        <v>-1</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>0</v>
@@ -5446,11 +5436,11 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Francis Texido</t>
+          <t>Brian Strange</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -5458,7 +5448,7 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.398</v>
+        <v>0.396</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>-3.4</v>
@@ -5473,11 +5463,11 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Jakob Guardado</t>
+          <t>Francis Texido</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
@@ -5485,13 +5475,13 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.402</v>
+        <v>0.398</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.5</v>
+        <v>-3.4</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>0</v>
@@ -5500,7 +5490,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Benny Thompson</t>
+          <t>Jakob Guardado</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
@@ -5512,9 +5502,11 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.396</v>
-      </c>
-      <c r="E14" s="4" t="inlineStr"/>
+        <v>0.402</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>-3.5</v>
+      </c>
       <c r="F14" s="4" t="n">
         <v>-1.2</v>
       </c>
@@ -5525,7 +5517,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Vincent Borghese</t>
+          <t>Benny Thompson</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
@@ -5537,11 +5529,9 @@
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.403</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-3.6</v>
-      </c>
+        <v>0.396</v>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="n">
         <v>-1.2</v>
       </c>
@@ -5552,11 +5542,11 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Andres Cova</t>
+          <t>Vincent Borghese</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
@@ -5564,10 +5554,10 @@
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.4</v>
+        <v>0.403</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.5</v>
+        <v>-3.6</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>-1.2</v>
@@ -5579,7 +5569,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Marco Vega</t>
+          <t>Andres Cova</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
@@ -5594,10 +5584,10 @@
         <v>0.4</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-4.2</v>
+        <v>-3.5</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.4</v>
+        <v>-1.2</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>0</v>
@@ -5606,27 +5596,54 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>Marco Vega</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
           <t>Nick Parker</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B19" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D19" s="4" t="n">
         <v>0.39</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E19" s="4" t="n">
         <v>-4.6</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F19" s="4" t="n">
         <v>-1.5</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9139,7 +9156,7 @@
     </row>
     <row r="33">
       <c r="A33" s="18" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
@@ -9148,27 +9165,23 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Anthony Scull</t>
+          <t>David Calabrese</t>
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.256</v>
+        <v>0.265</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.262</v>
+        <v>0.278</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.006</v>
+        <v>-0.013</v>
       </c>
       <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>swap from David Calabrese</t>
-        </is>
-      </c>
+      <c r="I33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="18" t="n">
@@ -9230,7 +9243,7 @@
     </row>
     <row r="36">
       <c r="A36" s="18" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
@@ -9239,20 +9252,20 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>David Calabrese</t>
+          <t>Kendrey Maduro</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.265</v>
+        <v>0.259</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.278</v>
+        <v>0.245</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-0.013</v>
+        <v>0.014</v>
       </c>
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="4" t="inlineStr">
@@ -9264,7 +9277,7 @@
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: 2.91</t>
+          <t>Est. R/G: 2.92</t>
         </is>
       </c>
     </row>
@@ -9320,11 +9333,11 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Arol Vera</t>
+          <t>David Mershon</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
@@ -9332,16 +9345,16 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.251</v>
+        <v>0.254</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.283</v>
+        <v>0.265</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.031</v>
+        <v>0.012</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.76</v>
+        <v>0.02</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
@@ -9357,28 +9370,28 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Anthony Scull</t>
+          <t>Gage Harrelson</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.262</v>
+        <v>0.242</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.288</v>
+        <v>0.307</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>0.025</v>
+        <v>0.066</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>2.54</v>
+        <v>3.02</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
@@ -9468,7 +9481,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Gage Harrelson</t>
+          <t>Kendrey Maduro</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
@@ -9480,16 +9493,16 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.242</v>
+        <v>0.245</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.307</v>
+        <v>0.295</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>0.066</v>
+        <v>0.05</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>3.02</v>
+        <v>2.32</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
@@ -9505,28 +9518,28 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Kendrey Maduro</t>
+          <t>Jake Munroe</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.245</v>
+        <v>0.228</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.295</v>
+        <v>0.309</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>0.05</v>
+        <v>0.081</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>2.32</v>
+        <v>-0.54</v>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
@@ -9542,28 +9555,28 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>David Mershon</t>
+          <t>Jonathan Linares</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.254</v>
+        <v>0.221</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.265</v>
+        <v>0.263</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>0.012</v>
+        <v>0.042</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
@@ -9598,7 +9611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9718,28 +9731,28 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Jake Munroe</t>
+          <t>Kyle West</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.228</v>
+        <v>0.245</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.309</v>
+        <v>0.285</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.081</v>
+        <v>0.041</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.54</v>
+        <v>-2.2</v>
       </c>
       <c r="I6" s="4" t="inlineStr"/>
     </row>
@@ -9973,28 +9986,28 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Jonathan Linares</t>
+          <t>Liordanys Menendez</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.221</v>
+        <v>0.216</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.263</v>
+        <v>0.309</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.042</v>
+        <v>0.093</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.04</v>
+        <v>2.79</v>
       </c>
       <c r="I13" s="4" t="inlineStr"/>
     </row>
@@ -10050,7 +10063,7 @@
     </row>
     <row r="16">
       <c r="A16" s="18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B16" s="18" t="inlineStr">
         <is>
@@ -10059,27 +10072,23 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Jonathan Linares</t>
+          <t>Dario Laverde</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
         <v>22</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.217</v>
+        <v>0.264</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.221</v>
+        <v>0.261</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>swap from Dario Laverde</t>
-        </is>
-      </c>
+      <c r="I16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="18" t="n">
@@ -10092,27 +10101,23 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Theo Gillen</t>
+          <t>Kyle West</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E17" s="4" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="F17" s="4" t="n">
         <v>0.245</v>
       </c>
-      <c r="F17" s="4" t="n">
-        <v>0.237</v>
-      </c>
       <c r="G17" s="4" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>swap from Jake Munroe</t>
-        </is>
-      </c>
+      <c r="I17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="18" t="n">
@@ -10277,7 +10282,7 @@
     </row>
     <row r="23">
       <c r="A23" s="18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
@@ -10310,7 +10315,7 @@
     </row>
     <row r="24">
       <c r="A24" s="18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
@@ -10319,32 +10324,32 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Dario Laverde</t>
+          <t>Theo Gillen</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.264</v>
+        <v>0.245</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.261</v>
+        <v>0.237</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="H24" s="4" t="n"/>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>swap from Jonathan Linares</t>
+          <t>swap from Liordanys Menendez</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: 2.15</t>
+          <t>Est. R/G: 2.26</t>
         </is>
       </c>
     </row>
@@ -10400,7 +10405,7 @@
     </row>
     <row r="28">
       <c r="A28" s="18" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
@@ -10409,27 +10414,23 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Jonathan Linares</t>
+          <t>Dario Laverde</t>
         </is>
       </c>
       <c r="D28" s="4" t="n">
         <v>22</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.229</v>
+        <v>0.255</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.221</v>
+        <v>0.261</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.008</v>
+        <v>-0.006</v>
       </c>
       <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>swap from Dario Laverde</t>
-        </is>
-      </c>
+      <c r="I28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="18" t="n">
@@ -10442,27 +10443,23 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Wyatt Vincent</t>
+          <t>Kyle West</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.232</v>
+        <v>0.237</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.213</v>
+        <v>0.245</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.019</v>
+        <v>-0.008</v>
       </c>
       <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>swap from Jake Munroe</t>
-        </is>
-      </c>
+      <c r="I29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="18" t="n">
@@ -10660,7 +10657,7 @@
     </row>
     <row r="36">
       <c r="A36" s="18" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
@@ -10669,32 +10666,32 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Dario Laverde</t>
+          <t>Wyatt Vincent</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.255</v>
+        <v>0.232</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.261</v>
+        <v>0.213</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-0.006</v>
+        <v>0.019</v>
       </c>
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>swap from Jonathan Linares</t>
+          <t>swap from Liordanys Menendez</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: 2.27</t>
+          <t>Est. R/G: 2.29</t>
         </is>
       </c>
     </row>
@@ -10713,18 +10710,32 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>-- empty --</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="4" t="n"/>
-      <c r="E39" s="4" t="n"/>
-      <c r="F39" s="4" t="n"/>
-      <c r="G39" s="4" t="n"/>
-      <c r="H39" s="4" t="n"/>
+          <t>Eliezer Rivero</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>-3.41</v>
+      </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>(no backup c candidate)</t>
+          <t>Backup C</t>
         </is>
       </c>
     </row>
@@ -10810,11 +10821,11 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Liordanys Menendez</t>
+          <t>Joswa Lugo</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
@@ -10822,16 +10833,16 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.216</v>
+        <v>0.213</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.309</v>
+        <v>0.3</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>0.093</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>2.79</v>
+        <v>2.26</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
@@ -10839,45 +10850,8 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="18" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Joswa Lugo</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>RF</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>0.213</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="20" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>Total: 13 players (target 13)</t>
         </is>
@@ -10903,7 +10877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10986,30 +10960,16 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Eliezer Rivero</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0.213</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>-3.41</v>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
+          <t>-- empty --</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
@@ -11052,28 +11012,28 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Victor Rodriguez</t>
+          <t>Alex Alicea</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.212</v>
+        <v>0.218</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.25</v>
+        <v>0.286</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.038</v>
+        <v>0.068</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.71</v>
+        <v>1.46</v>
       </c>
       <c r="I7" s="4" t="inlineStr"/>
     </row>
@@ -11085,7 +11045,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Alex Alicea</t>
+          <t>Charlie Meglio</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
@@ -11093,20 +11053,20 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.218</v>
+        <v>0.21</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.286</v>
+        <v>0.285</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.068</v>
+        <v>0.076</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.46</v>
+        <v>0.33</v>
       </c>
       <c r="I8" s="4" t="inlineStr"/>
     </row>
@@ -11221,11 +11181,11 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Randy De Jesus</t>
+          <t>Diego Tornes</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
@@ -11233,16 +11193,16 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.233</v>
+        <v>0.206</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.278</v>
+        <v>0.308</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.045</v>
+        <v>0.102</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.32</v>
+        <v>3.16</v>
       </c>
       <c r="I12" s="4" t="inlineStr"/>
     </row>
@@ -11330,9 +11290,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
-        <v>8</v>
-      </c>
+      <c r="A16" s="18" t="inlineStr"/>
       <c r="B16" s="18" t="inlineStr">
         <is>
           <t>C</t>
@@ -11340,21 +11298,13 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Eliezer Rivero</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>0.212</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>0.213</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>-0.001</v>
-      </c>
+          <t>-- empty --</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
       <c r="H16" s="4" t="n"/>
       <c r="I16" s="4" t="n"/>
     </row>
@@ -11389,7 +11339,7 @@
     </row>
     <row r="18">
       <c r="A18" s="18" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
@@ -11398,27 +11348,27 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Victor Rodriguez</t>
+          <t>Alex Alicea</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.211</v>
+        <v>0.215</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.212</v>
+        <v>0.218</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0</v>
+        <v>-0.003</v>
       </c>
       <c r="H18" s="4" t="n"/>
       <c r="I18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="18" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
@@ -11427,17 +11377,17 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Alex Alicea</t>
+          <t>Charlie Meglio</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
         <v>22</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.215</v>
+        <v>0.207</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.218</v>
+        <v>0.21</v>
       </c>
       <c r="G19" s="4" t="n">
         <v>-0.003</v>
@@ -11447,7 +11397,7 @@
     </row>
     <row r="20">
       <c r="A20" s="18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
@@ -11534,7 +11484,7 @@
     </row>
     <row r="23">
       <c r="A23" s="18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
@@ -11543,20 +11493,20 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Randy De Jesus</t>
+          <t>Diego Tornes</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.23</v>
+        <v>0.213</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.233</v>
+        <v>0.206</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.003</v>
+        <v>0.007</v>
       </c>
       <c r="H23" s="4" t="n"/>
       <c r="I23" s="4" t="n"/>
@@ -11593,7 +11543,7 @@
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: 1.34</t>
+          <t>Est. R/G: 1.15</t>
         </is>
       </c>
     </row>
@@ -11648,9 +11598,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
-        <v>8</v>
-      </c>
+      <c r="A28" s="18" t="inlineStr"/>
       <c r="B28" s="18" t="inlineStr">
         <is>
           <t>C</t>
@@ -11658,21 +11606,13 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Eliezer Rivero</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>0.213</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>0.003</v>
-      </c>
+          <t>-- empty --</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
       <c r="H28" s="4" t="n"/>
       <c r="I28" s="4" t="n"/>
     </row>
@@ -11707,7 +11647,7 @@
     </row>
     <row r="30">
       <c r="A30" s="18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
@@ -11716,20 +11656,20 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Victor Rodriguez</t>
+          <t>Alex Alicea</t>
         </is>
       </c>
       <c r="D30" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.212</v>
+        <v>0.225</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.212</v>
+        <v>0.218</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.001</v>
+        <v>0.007</v>
       </c>
       <c r="H30" s="4" t="n"/>
       <c r="I30" s="4" t="n"/>
@@ -11761,11 +11701,7 @@
         <v>0.006</v>
       </c>
       <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>swap from Alex Alicea</t>
-        </is>
-      </c>
+      <c r="I31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="18" t="n">
@@ -11798,7 +11734,7 @@
     </row>
     <row r="33">
       <c r="A33" s="18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
@@ -11807,20 +11743,20 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Alex Alicea</t>
+          <t>Blake Cyr</t>
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.225</v>
+        <v>0.23</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.218</v>
+        <v>0.206</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.007</v>
+        <v>0.024</v>
       </c>
       <c r="H33" s="4" t="n"/>
       <c r="I33" s="4" t="inlineStr">
@@ -11860,7 +11796,7 @@
     </row>
     <row r="35">
       <c r="A35" s="18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
@@ -11869,27 +11805,31 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Randy De Jesus</t>
+          <t>Junior Suriel</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.241</v>
+        <v>0.208</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.233</v>
+        <v>0.207</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.008</v>
+        <v>0.001</v>
       </c>
       <c r="H35" s="4" t="n"/>
-      <c r="I35" s="4" t="n"/>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>swap from Diego Tornes</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
@@ -11919,7 +11859,7 @@
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: 1.69</t>
+          <t>Est. R/G: 1.51</t>
         </is>
       </c>
     </row>
@@ -11961,28 +11901,28 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Charlie Meglio</t>
+          <t>Blake Cyr</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.21</v>
+        <v>0.206</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.285</v>
+        <v>0.296</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.076</v>
+        <v>0.09</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.33</v>
+        <v>1.72</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
@@ -12072,11 +12012,11 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Diego Tornes</t>
+          <t>Anthony Santa Cruz de Oviedo</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
@@ -12084,16 +12024,16 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.206</v>
+        <v>0.205</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.308</v>
+        <v>0.286</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>0.102</v>
+        <v>0.082</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>3.16</v>
+        <v>-1.85</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
@@ -12101,8 +12041,45 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="20" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>Depth</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Alexander Rincon</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Depth</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>Total: 13 players (target 13)</t>
         </is>
@@ -12244,28 +12221,28 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Anthony Santa Cruz de Oviedo</t>
+          <t>Sandy Ruiz</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.205</v>
+        <v>0.185</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.286</v>
+        <v>0.227</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.082</v>
+        <v>0.042</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.85</v>
+        <v>-5.3</v>
       </c>
       <c r="I6" s="4" t="inlineStr"/>
     </row>
@@ -12277,7 +12254,7 @@
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>Jeyson Horton</t>
+          <t>Victor Valdez</t>
         </is>
       </c>
       <c r="C7" s="23" t="n">
@@ -12285,20 +12262,20 @@
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E7" s="23" t="n">
-        <v>0.19</v>
+        <v>0.193</v>
       </c>
       <c r="F7" s="23" t="n">
-        <v>0.341</v>
+        <v>0.323</v>
       </c>
       <c r="G7" s="23" t="n">
-        <v>0.151</v>
+        <v>0.13</v>
       </c>
       <c r="H7" s="23" t="n">
-        <v>4.82</v>
+        <v>2.7</v>
       </c>
       <c r="I7" s="23" t="inlineStr">
         <is>
@@ -12307,41 +12284,37 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>3B</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>Victor Valdez</t>
-        </is>
-      </c>
-      <c r="C8" s="23" t="n">
-        <v>18</v>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>2B</t>
-        </is>
-      </c>
-      <c r="E8" s="23" t="n">
-        <v>0.193</v>
-      </c>
-      <c r="F8" s="23" t="n">
-        <v>0.323</v>
-      </c>
-      <c r="G8" s="23" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="H8" s="23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I8" s="23" t="inlineStr">
-        <is>
-          <t>High-potential prospect</t>
-        </is>
-      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Joan Sierra</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
@@ -12377,37 +12350,41 @@
       <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>LF</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Alexander Rincon</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Jeyson Horton</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="E10" s="4" t="n">
-        <v>0.202</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>0.287</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
+      <c r="E10" s="23" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="G10" s="23" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="H10" s="23" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>High-potential prospect</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
@@ -12589,7 +12566,7 @@
     </row>
     <row r="17">
       <c r="A17" s="18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
@@ -12598,27 +12575,27 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Anthony Santa Cruz de Oviedo</t>
+          <t>Sandy Ruiz</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.209</v>
+        <v>0.185</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.205</v>
+        <v>0.185</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
@@ -12627,7 +12604,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Jeyson Horton</t>
+          <t>Victor Valdez</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
@@ -12637,10 +12614,10 @@
         <v>0.19</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.19</v>
+        <v>0.193</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="H18" s="4" t="n"/>
       <c r="I18" s="4" t="n"/>
@@ -12656,20 +12633,20 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Victor Valdez</t>
+          <t>Joan Sierra</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E19" s="4" t="n">
         <v>0.19</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.193</v>
+        <v>0.196</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.002</v>
+        <v>-0.005</v>
       </c>
       <c r="H19" s="4" t="n"/>
       <c r="I19" s="4" t="n"/>
@@ -12705,7 +12682,7 @@
     </row>
     <row r="21">
       <c r="A21" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
@@ -12714,27 +12691,31 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Alexander Rincon</t>
+          <t>Greylin De La Paz</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.212</v>
+        <v>0.194</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.202</v>
+        <v>0.194</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.01</v>
+        <v>0.001</v>
       </c>
       <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>swap from Jeyson Horton</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
@@ -12743,27 +12724,31 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Yelinson Betances</t>
+          <t>Jeyson Horton</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.184</v>
+        <v>0.19</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.191</v>
+        <v>0.19</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.007</v>
+        <v>0</v>
       </c>
       <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>swap from Yelinson Betances</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
@@ -12772,27 +12757,31 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Greylin De La Paz</t>
+          <t>Yojancel Cabrera</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.194</v>
+        <v>0.19</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.194</v>
+        <v>0.186</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>swap from Greylin De La Paz</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
@@ -12822,7 +12811,7 @@
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: 0.38</t>
+          <t>Est. R/G: 0.23</t>
         </is>
       </c>
     </row>
@@ -12878,7 +12867,7 @@
     </row>
     <row r="28">
       <c r="A28" s="18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
@@ -12934,13 +12923,13 @@
       <c r="H29" s="4" t="n"/>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>swap from Anthony Santa Cruz de Oviedo</t>
+          <t>swap from Sandy Ruiz</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
@@ -12965,15 +12954,11 @@
         <v>0.005</v>
       </c>
       <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>swap from Jeyson Horton</t>
-        </is>
-      </c>
+      <c r="I30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="18" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
@@ -12982,31 +12967,27 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Cesar Paredes</t>
+          <t>Joan Sierra</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.184</v>
+        <v>0.208</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.177</v>
+        <v>0.196</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>swap from Victor Valdez</t>
-        </is>
-      </c>
+      <c r="I31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
@@ -13035,7 +13016,7 @@
     </row>
     <row r="33">
       <c r="A33" s="18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
@@ -13060,15 +13041,11 @@
         <v>0</v>
       </c>
       <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>swap from Alexander Rincon</t>
-        </is>
-      </c>
+      <c r="I33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
@@ -13097,7 +13074,7 @@
     </row>
     <row r="35">
       <c r="A35" s="18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
@@ -13126,7 +13103,7 @@
     </row>
     <row r="36">
       <c r="A36" s="18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
@@ -13135,20 +13112,20 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Byron Castillo</t>
+          <t>Humberto Tiberi</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.205</v>
+        <v>0.201</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.198</v>
+        <v>0.191</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="4" t="inlineStr">
@@ -13160,7 +13137,7 @@
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: 0.59</t>
+          <t>Est. R/G: 0.66</t>
         </is>
       </c>
     </row>
@@ -13364,11 +13341,11 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Byron Castillo</t>
+          <t>Jose Santana</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
@@ -13376,16 +13353,16 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.198</v>
+        <v>0.175</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.273</v>
+        <v>0.225</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>0.076</v>
+        <v>0.05</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>-2.33</v>
+        <v>-2.18</v>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
@@ -13496,41 +13473,37 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t>Angel Cervantes</t>
-        </is>
-      </c>
-      <c r="C5" s="23" t="n">
-        <v>16</v>
-      </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Yonathan Aro</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="23" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="F5" s="23" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="G5" s="23" t="n">
-        <v>0.192</v>
-      </c>
-      <c r="H5" s="23" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="I5" s="23" t="inlineStr">
-        <is>
-          <t>High-potential prospect</t>
-        </is>
-      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="18" t="inlineStr">
@@ -13540,28 +13513,28 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Yonathan Aro</t>
+          <t>Kason Siguenza</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.157</v>
+        <v>0.161</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.293</v>
+        <v>0.242</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.137</v>
+        <v>0.08</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2.15</v>
+        <v>-4.5</v>
       </c>
       <c r="I6" s="4" t="inlineStr"/>
     </row>
@@ -13606,7 +13579,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Joan Sierra</t>
+          <t>Josue Demey</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
@@ -13614,20 +13587,20 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.196</v>
+        <v>0.147</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.251</v>
+        <v>0.281</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.056</v>
+        <v>0.134</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-2.22</v>
+        <v>-0.28</v>
       </c>
       <c r="I8" s="4" t="inlineStr"/>
     </row>
@@ -13665,37 +13638,41 @@
       <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>LF</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Anyelo Marquez</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>RF</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>0.247</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>-0.98</v>
-      </c>
-      <c r="I10" s="4" t="inlineStr"/>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Angel Cervantes</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="G10" s="23" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="H10" s="23" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>High-potential prospect</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
@@ -13742,11 +13719,11 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Edwardo Espinal</t>
+          <t>Adrian Feliz</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
@@ -13754,16 +13731,16 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.203</v>
+        <v>0.11</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.247</v>
+        <v>0.264</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.045</v>
+        <v>0.154</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.38</v>
+        <v>0.62</v>
       </c>
       <c r="I12" s="4" t="inlineStr"/>
     </row>
@@ -13856,7 +13833,7 @@
     </row>
     <row r="16">
       <c r="A16" s="18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B16" s="18" t="inlineStr">
         <is>
@@ -13881,15 +13858,11 @@
         <v>0</v>
       </c>
       <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>swap from Angel Cervantes</t>
-        </is>
-      </c>
+      <c r="I16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="18" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
@@ -13898,31 +13871,27 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Jose Lavagnino</t>
+          <t>Kason Siguenza</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
         <v>19</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.156</v>
+        <v>0.164</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.143</v>
+        <v>0.161</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.012</v>
+        <v>0.002</v>
       </c>
       <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>swap from Yonathan Aro</t>
-        </is>
-      </c>
+      <c r="I17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
@@ -13951,7 +13920,7 @@
     </row>
     <row r="19">
       <c r="A19" s="18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
@@ -13960,27 +13929,27 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Joan Sierra</t>
+          <t>Josue Demey</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
         <v>20</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.19</v>
+        <v>0.144</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.196</v>
+        <v>0.147</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.005</v>
+        <v>-0.003</v>
       </c>
       <c r="H19" s="4" t="n"/>
       <c r="I19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
@@ -14009,7 +13978,7 @@
     </row>
     <row r="21">
       <c r="A21" s="18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
@@ -14018,27 +13987,31 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Anyelo Marquez</t>
+          <t>Jose Lavagnino</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.216</v>
+        <v>0.156</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.209</v>
+        <v>0.143</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>swap from Angel Cervantes</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
@@ -14071,7 +14044,7 @@
     </row>
     <row r="23">
       <c r="A23" s="18" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
@@ -14080,17 +14053,17 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Edwardo Espinal</t>
+          <t>Adrian Feliz</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.201</v>
+        <v>0.109</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.203</v>
+        <v>0.11</v>
       </c>
       <c r="G23" s="4" t="n">
         <v>-0.001</v>
@@ -14100,7 +14073,7 @@
     </row>
     <row r="24">
       <c r="A24" s="18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
@@ -14134,7 +14107,7 @@
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: -0.46</t>
+          <t>Est. R/G: -1.20</t>
         </is>
       </c>
     </row>
@@ -14190,7 +14163,7 @@
     </row>
     <row r="28">
       <c r="A28" s="18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
@@ -14215,15 +14188,11 @@
         <v>0</v>
       </c>
       <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="inlineStr">
-        <is>
-          <t>swap from Angel Cervantes</t>
-        </is>
-      </c>
+      <c r="I28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="18" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
@@ -14232,31 +14201,27 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Richard Trujillo</t>
+          <t>Kason Siguenza</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.125</v>
+        <v>0.156</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.125</v>
+        <v>0.161</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>swap from Yonathan Aro</t>
-        </is>
-      </c>
+      <c r="I29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
@@ -14285,7 +14250,7 @@
     </row>
     <row r="31">
       <c r="A31" s="18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
@@ -14294,27 +14259,27 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Joan Sierra</t>
+          <t>Josue Demey</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
         <v>20</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.208</v>
+        <v>0.154</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.196</v>
+        <v>0.147</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.012</v>
+        <v>0.007</v>
       </c>
       <c r="H31" s="4" t="n"/>
       <c r="I31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
@@ -14343,7 +14308,7 @@
     </row>
     <row r="33">
       <c r="A33" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
@@ -14352,27 +14317,31 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Anyelo Marquez</t>
+          <t>Roberto Martinez</t>
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.194</v>
+        <v>0.164</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.209</v>
+        <v>0.13</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.015</v>
+        <v>0.034</v>
       </c>
       <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="n"/>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>swap from Angel Cervantes</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="18" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
@@ -14381,31 +14350,27 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Roberto Martinez</t>
+          <t>Manny Guillen</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
         <v>17</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.164</v>
+        <v>0.128</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.13</v>
+        <v>0.128</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="H34" s="4" t="n"/>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>swap from Manny Guillen</t>
-        </is>
-      </c>
+      <c r="I34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="18" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
@@ -14414,27 +14379,27 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Edwardo Espinal</t>
+          <t>Adrian Feliz</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.206</v>
+        <v>0.112</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.203</v>
+        <v>0.11</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H35" s="4" t="n"/>
       <c r="I35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
@@ -14468,7 +14433,7 @@
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: -0.44</t>
+          <t>Est. R/G: -1.15</t>
         </is>
       </c>
     </row>

--- a/outputs/LAA_roster_system.xlsx
+++ b/outputs/LAA_roster_system.xlsx
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>2</v>
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-0.3</v>
+        <v>-0.32</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.61</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="6">
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-1.82</v>
+        <v>-1.05</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.79</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="7">
@@ -786,7 +786,7 @@
         <v>13</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.54</v>
+        <v>-2.38</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="8">
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.92</v>
+        <v>-3.88</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="9">
@@ -879,10 +879,10 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-6.14</v>
+        <v>-6.44</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.13</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="14">
@@ -4013,7 +4013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4118,11 +4118,11 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Arol Vera</t>
+          <t>Blake Cyr</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -4131,24 +4131,24 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.5</v>
+        <v>-3.7</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Tucker Flint</t>
+          <t>Alec Gomez</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -4157,76 +4157,76 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.3</v>
+        <v>-2.1</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Anthony Scull</t>
+          <t>Randy De Jesus</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.3</v>
+        <v>-1.7</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Alec Gomez</t>
+          <t>John Wimmer</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.1</v>
+        <v>-4.2</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Randy De Jesus</t>
+          <t>Brody Hopkins</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -4235,50 +4235,50 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.7</v>
+        <v>-3.9</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>John Wimmer</t>
+          <t>Harold Coll</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-4.2</v>
+        <v>-3.3</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.5</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Brody Hopkins</t>
+          <t>Edwardo Espinal</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
@@ -4287,28 +4287,28 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.9</v>
+        <v>-3.4</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.1</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Harold Coll</t>
+          <t>Jonny McGill</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -4317,68 +4317,68 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.3</v>
+        <v>-4.8</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.9</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Edwardo Espinal</t>
+          <t>Nick Rodriguez</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.4</v>
+        <v>-5.1</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.9</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Jonny McGill</t>
+          <t>Anyelo Marquez</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-4.8</v>
+        <v>-3.5</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.2</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Nick Rodriguez</t>
+          <t>Ryland Zaborowski</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -4395,20 +4395,20 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-5.1</v>
+        <v>-5.4</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.3</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Anyelo Marquez</t>
+          <t>Adonanfer Reyes</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
@@ -4417,72 +4417,72 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>R(DLR)</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-3.5</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.4</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Ryland Zaborowski</t>
+          <t>Omar Martinez</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-5.4</v>
+        <v>-4.1</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.5</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Adonanfer Reyes</t>
+          <t>Slate Alford</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>R(DLR)</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-8.199999999999999</v>
+        <v>-4.8</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.6</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Omar Martinez</t>
+          <t>Cole Fontenelle</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
@@ -4490,29 +4490,29 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-4.1</v>
+        <v>-4.8</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.7</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Slate Alford</t>
+          <t>Samuel Capellan</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
@@ -4521,20 +4521,20 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-4.8</v>
+        <v>-6.8</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.8</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Cole Fontenelle</t>
+          <t>Alberto Rios</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -4551,20 +4551,20 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-4.8</v>
+        <v>-5.5</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.9</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Samuel Capellan</t>
+          <t>Ray Garrett</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
@@ -4573,102 +4573,102 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-6.8</v>
+        <v>-6.5</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.9</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Alberto Rios</t>
+          <t>Ashten Wong</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-5.5</v>
+        <v>-7.2</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Ray Garrett</t>
+          <t>Kyle West</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-6.5</v>
+        <v>-4.4</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Ashten Wong</t>
+          <t>Will Hodo</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-7.2</v>
+        <v>-6</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-2.1</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Will Hodo</t>
+          <t>Zack Stewart</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
@@ -4677,37 +4677,37 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-2.3</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Zack Stewart</t>
+          <t>Luis Bruno</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>R(DLR)</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-7</v>
+        <v>-11.6</v>
       </c>
       <c r="F28" s="4" t="n">
         <v>-2.5</v>
@@ -4716,37 +4716,37 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Luis Bruno</t>
+          <t>Byron Castillo</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>R(DLR)</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-11.6</v>
+        <v>-6.9</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-2.5</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Byron Castillo</t>
+          <t>Alver Medina</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
@@ -4755,63 +4755,63 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>R(DLR)</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-6.9</v>
+        <v>-7.9</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-2.7</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Alver Medina</t>
+          <t>Luis Rodriguez</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>R(DLR)</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-7.9</v>
+        <v>-4.7</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-2.9</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Luis Rodriguez</t>
+          <t>Victor Rodriguez</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-4.7</v>
+        <v>-5.1</v>
       </c>
       <c r="F32" s="4" t="n">
         <v>-3</v>
@@ -4820,27 +4820,27 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Victor Rodriguez</t>
+          <t>Jonathan Linares</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-5.1</v>
+        <v>-5.5</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-3</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="34">
@@ -4924,41 +4924,41 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Mike Escolero</t>
+          <t>Eliezer Rivero</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>R(DLR)</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>-11.7</v>
+        <v>-6.4</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>-3.9</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Diego Rondon</t>
+          <t>Mike Escolero</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -4967,50 +4967,50 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>-11.2</v>
+        <v>-11.7</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>-4.4</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Bryan Martinez</t>
+          <t>Diego Rondon</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>R(DLR)</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>-7.3</v>
+        <v>-11.2</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>-4.5</v>
+        <v>-4.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Diego Felix</t>
+          <t>Bryan Martinez</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -5019,50 +5019,50 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>-8.699999999999999</v>
+        <v>-7.3</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>-4.8</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Salvatore Cruz</t>
+          <t>Diego Felix</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>DH</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>R(DLR)</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>-12.6</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>-5.1</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>David Manzueta</t>
+          <t>Salvatore Cruz</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -5071,24 +5071,24 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>-10.5</v>
+        <v>-12.6</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>-5.2</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Drew Lafferty</t>
+          <t>David Manzueta</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -5097,16 +5097,16 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>-12.3</v>
+        <v>-10.5</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>-6.2</v>
+        <v>-5.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Walker Polk</t>
+          <t>Drew Lafferty</t>
         </is>
       </c>
       <c r="B44" s="4" t="n">
@@ -5123,7 +5123,7 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>-13.3</v>
+        <v>-12.3</v>
       </c>
       <c r="F44" s="4" t="n">
         <v>-6.2</v>
@@ -5132,26 +5132,52 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
+          <t>Walker Polk</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>R(DLR)</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>-13.3</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>-6.2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
           <t>Kaden Hopson</t>
         </is>
       </c>
-      <c r="B45" s="4" t="n">
+      <c r="B46" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>A+</t>
         </is>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E46" s="4" t="n">
         <v>-6.5</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="F46" s="4" t="n">
         <v>-6.4</v>
       </c>
     </row>
@@ -8165,18 +8191,32 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>-- empty --</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
+          <t>Arol Vera</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>0.06</v>
+      </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>(no utility if candidate)</t>
+          <t>Utility IF</t>
         </is>
       </c>
     </row>
@@ -8188,18 +8228,32 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>-- empty --</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="4" t="n"/>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="n"/>
+          <t>Anthony Scull</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>1.14</v>
+      </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>(no utility of candidate)</t>
+          <t>Utility OF</t>
         </is>
       </c>
     </row>
@@ -8211,25 +8265,39 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>-- empty --</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="4" t="n"/>
+          <t>Tucker Flint</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>0.16</v>
+      </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>(no best bat candidate)</t>
+          <t>Best bat</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="20" t="inlineStr">
         <is>
-          <t>Total: 10 players (target 13)</t>
+          <t>Total: 13 players (target 13)</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9333,11 +9401,11 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>David Mershon</t>
+          <t>Kendrey Maduro</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
@@ -9345,16 +9413,16 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.254</v>
+        <v>0.245</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.265</v>
+        <v>0.295</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.012</v>
+        <v>0.05</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.02</v>
+        <v>2.32</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
@@ -9436,158 +9504,10 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="18" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Jose Camacho</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>1B</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>0.223</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>0.313</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
-      </c>
-    </row>
     <row r="44">
-      <c r="A44" s="18" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>Kendrey Maduro</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>RF</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="18" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Jake Munroe</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>0.228</v>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>0.309</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="H45" s="4" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="18" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Jonathan Linares</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>0.221</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>0.263</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>Total: 17 players (target 13)</t>
+      <c r="A44" s="20" t="inlineStr">
+        <is>
+          <t>Total: 13 players (target 13)</t>
         </is>
       </c>
     </row>
@@ -9611,7 +9531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9731,11 +9651,11 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Kyle West</t>
+          <t>Jose Camacho</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
@@ -9743,16 +9663,16 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.245</v>
+        <v>0.223</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.285</v>
+        <v>0.313</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.041</v>
+        <v>0.091</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-2.2</v>
+        <v>-0.6</v>
       </c>
       <c r="I6" s="4" t="inlineStr"/>
     </row>
@@ -9986,11 +9906,11 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Liordanys Menendez</t>
+          <t>David Mershon</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
@@ -9998,16 +9918,16 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.216</v>
+        <v>0.254</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.309</v>
+        <v>0.265</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.093</v>
+        <v>0.012</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.79</v>
+        <v>0.02</v>
       </c>
       <c r="I13" s="4" t="inlineStr"/>
     </row>
@@ -10092,7 +10012,7 @@
     </row>
     <row r="17">
       <c r="A17" s="18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
@@ -10101,23 +10021,27 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Kyle West</t>
+          <t>Theo Gillen</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.249</v>
+        <v>0.245</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.245</v>
+        <v>0.237</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>swap from Jose Camacho</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="18" t="n">
@@ -10150,7 +10074,7 @@
     </row>
     <row r="19">
       <c r="A19" s="18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
@@ -10159,31 +10083,27 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Ronny Cruz</t>
+          <t>Gavin Fien</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
         <v>20</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.251</v>
+        <v>0.235</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.251</v>
+        <v>0.242</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0</v>
+        <v>-0.008</v>
       </c>
       <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>swap from Gavin Fien</t>
-        </is>
-      </c>
+      <c r="I19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
@@ -10192,27 +10112,23 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Ivan Tatis</t>
+          <t>Ronny Cruz</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
         <v>20</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.205</v>
+        <v>0.251</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.21</v>
+        <v>0.251</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>swap from Ronny Cruz</t>
-        </is>
-      </c>
+      <c r="I20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="18" t="n">
@@ -10282,7 +10198,7 @@
     </row>
     <row r="23">
       <c r="A23" s="18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
@@ -10291,20 +10207,20 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Gavin Fien</t>
+          <t>David Mershon</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.235</v>
+        <v>0.254</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.242</v>
+        <v>0.254</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.008</v>
+        <v>0</v>
       </c>
       <c r="H23" s="4" t="n"/>
       <c r="I23" s="4" t="inlineStr">
@@ -10315,7 +10231,7 @@
     </row>
     <row r="24">
       <c r="A24" s="18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
@@ -10324,32 +10240,32 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Theo Gillen</t>
+          <t>Jake Munroe</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.245</v>
+        <v>0.228</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.237</v>
+        <v>0.228</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="H24" s="4" t="n"/>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>swap from Liordanys Menendez</t>
+          <t>swap from David Mershon</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: 2.26</t>
+          <t>Est. R/G: 2.36</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10350,7 @@
     </row>
     <row r="29">
       <c r="A29" s="18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
@@ -10443,27 +10359,27 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Kyle West</t>
+          <t>Jose Camacho</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.237</v>
+        <v>0.231</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.245</v>
+        <v>0.223</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.008</v>
+        <v>0.008</v>
       </c>
       <c r="H29" s="4" t="n"/>
       <c r="I29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
@@ -10492,7 +10408,7 @@
     </row>
     <row r="31">
       <c r="A31" s="18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
@@ -10501,31 +10417,27 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Ronny Cruz</t>
+          <t>Gavin Fien</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
         <v>20</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.251</v>
+        <v>0.26</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.251</v>
+        <v>0.242</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="inlineStr">
-        <is>
-          <t>swap from Gavin Fien</t>
-        </is>
-      </c>
+      <c r="I31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
@@ -10534,27 +10446,23 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Ivan Tatis</t>
+          <t>Ronny Cruz</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
         <v>20</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.221</v>
+        <v>0.251</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.21</v>
+        <v>0.251</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>swap from Ronny Cruz</t>
-        </is>
-      </c>
+      <c r="I32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="18" t="n">
@@ -10624,7 +10532,7 @@
     </row>
     <row r="35">
       <c r="A35" s="18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
@@ -10633,20 +10541,20 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Gavin Fien</t>
+          <t>Wyatt Vincent</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
         <v>20</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.26</v>
+        <v>0.232</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.242</v>
+        <v>0.213</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.018</v>
+        <v>0.019</v>
       </c>
       <c r="H35" s="4" t="n"/>
       <c r="I35" s="4" t="inlineStr">
@@ -10657,7 +10565,7 @@
     </row>
     <row r="36">
       <c r="A36" s="18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
@@ -10666,32 +10574,28 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Wyatt Vincent</t>
+          <t>David Mershon</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.232</v>
+        <v>0.254</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.213</v>
+        <v>0.254</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="H36" s="4" t="n"/>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>swap from Liordanys Menendez</t>
-        </is>
-      </c>
+      <c r="I36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: 2.29</t>
+          <t>Est. R/G: 2.39</t>
         </is>
       </c>
     </row>
@@ -10710,32 +10614,18 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Eliezer Rivero</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>0.213</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>-3.41</v>
-      </c>
+          <t>-- empty --</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>Backup C</t>
+          <t>(no backup c candidate)</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10637,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Ivan Tatis</t>
+          <t>Joswa Lugo</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
@@ -10755,20 +10645,20 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.21</v>
+        <v>0.213</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.287</v>
+        <v>0.3</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.077</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>3.26</v>
+        <v>2.26</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
@@ -10821,11 +10711,11 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Joswa Lugo</t>
+          <t>Liordanys Menendez</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
@@ -10833,16 +10723,16 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.213</v>
+        <v>0.216</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.3</v>
+        <v>0.309</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>2.26</v>
+        <v>2.79</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
@@ -10850,8 +10740,45 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="20" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>Depth</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Jake Munroe</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>Depth</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>Total: 13 players (target 13)</t>
         </is>
@@ -11045,11 +10972,11 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Charlie Meglio</t>
+          <t>Ivan Tatis</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
@@ -11060,13 +10987,13 @@
         <v>0.21</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.285</v>
+        <v>0.287</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.076</v>
+        <v>0.077</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.33</v>
+        <v>3.26</v>
       </c>
       <c r="I8" s="4" t="inlineStr"/>
     </row>
@@ -11377,20 +11304,20 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Charlie Meglio</t>
+          <t>Ivan Tatis</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.207</v>
+        <v>0.205</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>0.21</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.003</v>
+        <v>-0.005</v>
       </c>
       <c r="H19" s="4" t="n"/>
       <c r="I19" s="4" t="n"/>
@@ -11543,7 +11470,7 @@
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: 1.15</t>
+          <t>Est. R/G: 1.14</t>
         </is>
       </c>
     </row>
@@ -11647,7 +11574,7 @@
     </row>
     <row r="30">
       <c r="A30" s="18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
@@ -11676,7 +11603,7 @@
     </row>
     <row r="31">
       <c r="A31" s="18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
@@ -11685,27 +11612,27 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Charlie Meglio</t>
+          <t>Ivan Tatis</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.216</v>
+        <v>0.221</v>
       </c>
       <c r="F31" s="4" t="n">
         <v>0.21</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.006</v>
+        <v>0.011</v>
       </c>
       <c r="H31" s="4" t="n"/>
       <c r="I31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
@@ -11734,7 +11661,7 @@
     </row>
     <row r="33">
       <c r="A33" s="18" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
@@ -11743,20 +11670,20 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Blake Cyr</t>
+          <t>Junior Suriel</t>
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.23</v>
+        <v>0.208</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.206</v>
+        <v>0.207</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.024</v>
+        <v>0.001</v>
       </c>
       <c r="H33" s="4" t="n"/>
       <c r="I33" s="4" t="inlineStr">
@@ -11796,7 +11723,7 @@
     </row>
     <row r="35">
       <c r="A35" s="18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
@@ -11805,20 +11732,20 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Junior Suriel</t>
+          <t>Enzo Paulino</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.208</v>
+        <v>0.213</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.207</v>
+        <v>0.231</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.001</v>
+        <v>-0.018</v>
       </c>
       <c r="H35" s="4" t="n"/>
       <c r="I35" s="4" t="inlineStr">
@@ -11859,7 +11786,7 @@
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: 1.51</t>
+          <t>Est. R/G: 1.47</t>
         </is>
       </c>
     </row>
@@ -11901,28 +11828,28 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Blake Cyr</t>
+          <t>Charlie Meglio</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.206</v>
+        <v>0.21</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.296</v>
+        <v>0.285</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.09</v>
+        <v>0.076</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.72</v>
+        <v>0.33</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>

--- a/outputs/LAA_roster_system.xlsx
+++ b/outputs/LAA_roster_system.xlsx
@@ -714,7 +714,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>3.12</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="5">
@@ -738,7 +738,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>-0.32</v>
+        <v>-0.55</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0.73</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="6">
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-1.05</v>
+        <v>-1.1</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="7">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-2.38</v>
+        <v>-2.25</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="8">
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.88</v>
+        <v>-3.92</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="9">
@@ -6864,23 +6864,27 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Jake Mangum</t>
+          <t>Bryce Teodosio</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.298</v>
+        <v>0.293</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.309</v>
+        <v>0.295</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.01</v>
+        <v>-0.002</v>
       </c>
       <c r="H34" s="4" t="n"/>
-      <c r="I34" s="4" t="n"/>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>swap from Jake Mangum</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="18" t="n">
@@ -6922,20 +6926,20 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Gustavo Campero</t>
+          <t>Cooper Ingle</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.314</v>
+        <v>0.304</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.314</v>
+        <v>0.324</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="4" t="inlineStr">
@@ -6947,7 +6951,7 @@
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: 5.11</t>
+          <t>Est. R/G: 5.05</t>
         </is>
       </c>
     </row>
@@ -7040,28 +7044,28 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Gustavo Campero</t>
+          <t>Bryce Teodosio</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.314</v>
+        <v>0.295</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>0.314</v>
+        <v>0.295</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>0.5</v>
+        <v>3.94</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
@@ -7235,28 +7239,28 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Ben Gobbel</t>
+          <t>Gustavo Campero</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.286</v>
+        <v>0.314</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.285</v>
+        <v>0.314</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-1.91</v>
+        <v>0.5</v>
       </c>
       <c r="I6" s="4" t="inlineStr"/>
     </row>
@@ -7364,74 +7368,74 @@
       <c r="I9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>LF</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Wade Meckler</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>CF</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Nelson Rada</t>
         </is>
       </c>
-      <c r="C10" s="23" t="n">
+      <c r="C11" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E11" s="23" t="n">
         <v>0.288</v>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F11" s="23" t="n">
         <v>0.334</v>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="G11" s="23" t="n">
         <v>0.046</v>
       </c>
-      <c r="H10" s="23" t="n">
+      <c r="H11" s="23" t="n">
         <v>2.54</v>
       </c>
-      <c r="I10" s="23" t="inlineStr">
+      <c r="I11" s="23" t="inlineStr">
         <is>
           <t>High-potential prospect</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>CF</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Bryce Teodosio</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>CF</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="I11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
@@ -7441,7 +7445,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Wade Meckler</t>
+          <t>Tucker Flint</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
@@ -7453,16 +7457,16 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.305</v>
+        <v>0.264</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.318</v>
+        <v>0.289</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.013</v>
+        <v>0.025</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.32</v>
+        <v>0.16</v>
       </c>
       <c r="I12" s="4" t="inlineStr"/>
     </row>
@@ -7580,7 +7584,7 @@
     </row>
     <row r="17">
       <c r="A17" s="18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B17" s="18" t="inlineStr">
         <is>
@@ -7589,20 +7593,20 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Ben Gobbel</t>
+          <t>Gustavo Campero</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.285</v>
+        <v>0.314</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.286</v>
+        <v>0.314</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="n"/>
@@ -7638,7 +7642,7 @@
     </row>
     <row r="19">
       <c r="A19" s="18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
@@ -7667,7 +7671,7 @@
     </row>
     <row r="20">
       <c r="A20" s="18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
@@ -7696,7 +7700,7 @@
     </row>
     <row r="21">
       <c r="A21" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B21" s="18" t="inlineStr">
         <is>
@@ -7705,20 +7709,20 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Nelson Rada</t>
+          <t>Wade Meckler</t>
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.296</v>
+        <v>0.31</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.288</v>
+        <v>0.305</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="H21" s="4" t="n"/>
       <c r="I21" s="4" t="n"/>
@@ -7734,27 +7738,27 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Bryce Teodosio</t>
+          <t>Nelson Rada</t>
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.295</v>
+        <v>0.296</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.295</v>
+        <v>0.288</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H22" s="4" t="n"/>
       <c r="I22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="18" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
@@ -7763,17 +7767,17 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Wade Meckler</t>
+          <t>Tucker Flint</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
         <v>26</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.31</v>
+        <v>0.269</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.305</v>
+        <v>0.264</v>
       </c>
       <c r="G23" s="4" t="n">
         <v>0.005</v>
@@ -7813,7 +7817,7 @@
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: 3.86</t>
+          <t>Est. R/G: 3.87</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7873,7 @@
     </row>
     <row r="28">
       <c r="A28" s="18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
@@ -7927,7 +7931,11 @@
         <v>0.001</v>
       </c>
       <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="n"/>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>swap from Gustavo Campero</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="18" t="n">
@@ -7960,7 +7968,7 @@
     </row>
     <row r="31">
       <c r="A31" s="18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
@@ -7969,27 +7977,31 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Rubel Cespedes</t>
+          <t>Jim Jarvis</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
         <v>26</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.274</v>
+        <v>0.277</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.296</v>
+        <v>0.292</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.023</v>
+        <v>-0.015</v>
       </c>
       <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>swap from Rubel Cespedes</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
@@ -7998,23 +8010,27 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Jim Jarvis</t>
+          <t>Capri Ortiz</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.277</v>
+        <v>0.26</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.292</v>
+        <v>0.247</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.015</v>
+        <v>0.012</v>
       </c>
       <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>swap from Jim Jarvis</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="18" t="n">
@@ -8027,27 +8043,31 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Nelson Rada</t>
+          <t>Anthony Scull</t>
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.268</v>
+        <v>0.256</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.288</v>
+        <v>0.262</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.02</v>
+        <v>-0.006</v>
       </c>
       <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="n"/>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>swap from Wade Meckler</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
@@ -8056,27 +8076,27 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Bryce Teodosio</t>
+          <t>Nelson Rada</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.293</v>
+        <v>0.268</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.295</v>
+        <v>0.288</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.002</v>
+        <v>-0.02</v>
       </c>
       <c r="H34" s="4" t="n"/>
       <c r="I34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
@@ -8101,11 +8121,15 @@
         <v>-0.012</v>
       </c>
       <c r="H35" s="4" t="n"/>
-      <c r="I35" s="4" t="n"/>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>swap from Tucker Flint</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
@@ -8114,28 +8138,32 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Niko Kavadas</t>
+          <t>Gustavo Campero</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.28</v>
+        <v>0.314</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.291</v>
+        <v>0.314</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-0.011</v>
+        <v>0</v>
       </c>
       <c r="H36" s="4" t="n"/>
-      <c r="I36" s="4" t="n"/>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>swap from Niko Kavadas</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: 3.44</t>
+          <t>Est. R/G: 3.39</t>
         </is>
       </c>
     </row>
@@ -8191,28 +8219,28 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Arol Vera</t>
+          <t>Capri Ortiz</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.251</v>
+        <v>0.247</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.283</v>
+        <v>0.282</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.031</v>
+        <v>0.034</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>0.06</v>
+        <v>2.87</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
@@ -8265,28 +8293,28 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Tucker Flint</t>
+          <t>Ben Gobbel</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.264</v>
+        <v>0.286</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.289</v>
+        <v>0.285</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>0.025</v>
+        <v>-0.001</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>0.16</v>
+        <v>-1.91</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
@@ -8544,11 +8572,11 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Capri Ortiz</t>
+          <t>Felix Morrobel</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
@@ -8556,16 +8584,16 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.247</v>
+        <v>0.218</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.282</v>
+        <v>0.265</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.034</v>
+        <v>0.047</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.87</v>
+        <v>4.33</v>
       </c>
       <c r="I9" s="4" t="inlineStr"/>
     </row>
@@ -8882,20 +8910,20 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Capri Ortiz</t>
+          <t>Felix Morrobel</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.242</v>
+        <v>0.214</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.247</v>
+        <v>0.218</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.005</v>
+        <v>-0.004</v>
       </c>
       <c r="H20" s="4" t="n"/>
       <c r="I20" s="4" t="n"/>
@@ -9019,7 +9047,7 @@
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: 3.07</t>
+          <t>Est. R/G: 2.97</t>
         </is>
       </c>
     </row>
@@ -9075,7 +9103,7 @@
     </row>
     <row r="28">
       <c r="A28" s="18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
@@ -9195,7 +9223,7 @@
     </row>
     <row r="32">
       <c r="A32" s="18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
@@ -9204,20 +9232,20 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Capri Ortiz</t>
+          <t>Felix Morrobel</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.26</v>
+        <v>0.226</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.247</v>
+        <v>0.218</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
       <c r="H32" s="4" t="n"/>
       <c r="I32" s="4" t="n"/>
@@ -9311,7 +9339,7 @@
     </row>
     <row r="36">
       <c r="A36" s="18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
@@ -9320,20 +9348,20 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Kendrey Maduro</t>
+          <t>Gabriel Davalillo</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.259</v>
+        <v>0.253</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>0.245</v>
+        <v>0.254</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>0.014</v>
+        <v>-0.001</v>
       </c>
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="4" t="inlineStr">
@@ -9345,7 +9373,7 @@
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: 2.92</t>
+          <t>Est. R/G: 2.77</t>
         </is>
       </c>
     </row>
@@ -9401,11 +9429,11 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Kendrey Maduro</t>
+          <t>Arol Vera</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
@@ -9413,16 +9441,16 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.245</v>
+        <v>0.251</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.295</v>
+        <v>0.283</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.05</v>
+        <v>0.031</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>2.32</v>
+        <v>1.76</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
@@ -9651,28 +9679,28 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Jose Camacho</t>
+          <t>Kendrey Maduro</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.223</v>
+        <v>0.245</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.313</v>
+        <v>0.295</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.091</v>
+        <v>0.05</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.6</v>
+        <v>2.32</v>
       </c>
       <c r="I6" s="4" t="inlineStr"/>
     </row>
@@ -10039,7 +10067,7 @@
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>swap from Jose Camacho</t>
+          <t>swap from Kendrey Maduro</t>
         </is>
       </c>
     </row>
@@ -10074,7 +10102,7 @@
     </row>
     <row r="19">
       <c r="A19" s="18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
@@ -10083,27 +10111,31 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Gavin Fien</t>
+          <t>Ronny Cruz</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
         <v>20</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.235</v>
+        <v>0.251</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.242</v>
+        <v>0.251</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.008</v>
+        <v>0</v>
       </c>
       <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>swap from Gavin Fien</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
@@ -10112,23 +10144,27 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Ronny Cruz</t>
+          <t>Ivan Tatis</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
         <v>20</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.251</v>
+        <v>0.205</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.251</v>
+        <v>0.21</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>swap from Ronny Cruz</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="18" t="n">
@@ -10198,7 +10234,7 @@
     </row>
     <row r="23">
       <c r="A23" s="18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B23" s="18" t="inlineStr">
         <is>
@@ -10207,20 +10243,20 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>David Mershon</t>
+          <t>Kendrey Maduro</t>
         </is>
       </c>
       <c r="D23" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.254</v>
+        <v>0.239</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.254</v>
+        <v>0.245</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0</v>
+        <v>-0.006</v>
       </c>
       <c r="H23" s="4" t="n"/>
       <c r="I23" s="4" t="inlineStr">
@@ -10231,7 +10267,7 @@
     </row>
     <row r="24">
       <c r="A24" s="18" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
@@ -10240,32 +10276,28 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Jake Munroe</t>
+          <t>David Mershon</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
         <v>23</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.228</v>
+        <v>0.254</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.228</v>
+        <v>0.254</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>swap from David Mershon</t>
-        </is>
-      </c>
+      <c r="I24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: 2.36</t>
+          <t>Est. R/G: 2.30</t>
         </is>
       </c>
     </row>
@@ -10321,7 +10353,7 @@
     </row>
     <row r="28">
       <c r="A28" s="18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
@@ -10350,7 +10382,7 @@
     </row>
     <row r="29">
       <c r="A29" s="18" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
@@ -10359,27 +10391,27 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Jose Camacho</t>
+          <t>Kendrey Maduro</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.231</v>
+        <v>0.259</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.223</v>
+        <v>0.245</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.008</v>
+        <v>0.014</v>
       </c>
       <c r="H29" s="4" t="n"/>
       <c r="I29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
@@ -10408,7 +10440,7 @@
     </row>
     <row r="31">
       <c r="A31" s="18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
@@ -10417,27 +10449,31 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Gavin Fien</t>
+          <t>Ronny Cruz</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
         <v>20</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.26</v>
+        <v>0.251</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.242</v>
+        <v>0.251</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>swap from Gavin Fien</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
@@ -10446,27 +10482,31 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Ronny Cruz</t>
+          <t>Ivan Tatis</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
         <v>20</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.251</v>
+        <v>0.221</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.251</v>
+        <v>0.21</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>swap from Ronny Cruz</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
@@ -10532,7 +10572,7 @@
     </row>
     <row r="35">
       <c r="A35" s="18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
@@ -10541,20 +10581,20 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Wyatt Vincent</t>
+          <t>Gavin Fien</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
         <v>20</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.232</v>
+        <v>0.26</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.213</v>
+        <v>0.242</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.019</v>
+        <v>0.018</v>
       </c>
       <c r="H35" s="4" t="n"/>
       <c r="I35" s="4" t="inlineStr">
@@ -10565,7 +10605,7 @@
     </row>
     <row r="36">
       <c r="A36" s="18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
@@ -10595,7 +10635,7 @@
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: 2.39</t>
+          <t>Est. R/G: 2.46</t>
         </is>
       </c>
     </row>
@@ -10637,7 +10677,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Joswa Lugo</t>
+          <t>Ivan Tatis</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
@@ -10645,20 +10685,20 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.213</v>
+        <v>0.21</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>0.3</v>
+        <v>0.287</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>2.26</v>
+        <v>3.26</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
@@ -10711,28 +10751,28 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Liordanys Menendez</t>
+          <t>Jose Camacho</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.216</v>
+        <v>0.223</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.309</v>
+        <v>0.313</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>0.093</v>
+        <v>0.091</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>2.79</v>
+        <v>-0.6</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
@@ -10804,7 +10844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -10972,7 +11012,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Ivan Tatis</t>
+          <t>Joswa Lugo</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
@@ -10980,20 +11020,20 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.21</v>
+        <v>0.213</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.287</v>
+        <v>0.3</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.077</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.26</v>
+        <v>2.26</v>
       </c>
       <c r="I8" s="4" t="inlineStr"/>
     </row>
@@ -11005,11 +11045,11 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Felix Morrobel</t>
+          <t>Charlie Meglio</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
@@ -11017,16 +11057,16 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.218</v>
+        <v>0.21</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.265</v>
+        <v>0.285</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.047</v>
+        <v>0.076</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4.33</v>
+        <v>0.33</v>
       </c>
       <c r="I9" s="4" t="inlineStr"/>
     </row>
@@ -11108,11 +11148,11 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Diego Tornes</t>
+          <t>Liordanys Menendez</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
@@ -11120,16 +11160,16 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.206</v>
+        <v>0.216</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.308</v>
+        <v>0.309</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.102</v>
+        <v>0.093</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3.16</v>
+        <v>2.79</v>
       </c>
       <c r="I12" s="4" t="inlineStr"/>
     </row>
@@ -11295,7 +11335,7 @@
     </row>
     <row r="19">
       <c r="A19" s="18" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B19" s="18" t="inlineStr">
         <is>
@@ -11304,27 +11344,27 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Ivan Tatis</t>
+          <t>Joswa Lugo</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
         <v>20</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.205</v>
+        <v>0.213</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.21</v>
+        <v>0.213</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="H19" s="4" t="n"/>
       <c r="I19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="18" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
@@ -11333,20 +11373,20 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Felix Morrobel</t>
+          <t>Charlie Meglio</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.214</v>
+        <v>0.207</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.218</v>
+        <v>0.21</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.004</v>
+        <v>-0.003</v>
       </c>
       <c r="H20" s="4" t="n"/>
       <c r="I20" s="4" t="n"/>
@@ -11436,7 +11476,11 @@
         <v>0.007</v>
       </c>
       <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>swap from Liordanys Menendez</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="18" t="n">
@@ -11603,7 +11647,7 @@
     </row>
     <row r="31">
       <c r="A31" s="18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
@@ -11612,27 +11656,27 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Ivan Tatis</t>
+          <t>Joswa Lugo</t>
         </is>
       </c>
       <c r="D31" s="4" t="n">
         <v>20</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.221</v>
+        <v>0.213</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.21</v>
+        <v>0.213</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="H31" s="4" t="n"/>
       <c r="I31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
@@ -11641,20 +11685,20 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Felix Morrobel</t>
+          <t>Charlie Meglio</t>
         </is>
       </c>
       <c r="D32" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.226</v>
+        <v>0.216</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.218</v>
+        <v>0.21</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.008</v>
+        <v>0.006</v>
       </c>
       <c r="H32" s="4" t="n"/>
       <c r="I32" s="4" t="n"/>
@@ -11723,7 +11767,7 @@
     </row>
     <row r="35">
       <c r="A35" s="18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
@@ -11732,27 +11776,23 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Enzo Paulino</t>
+          <t>Liordanys Menendez</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.213</v>
+        <v>0.227</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.231</v>
+        <v>0.216</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.018</v>
+        <v>0.011</v>
       </c>
       <c r="H35" s="4" t="n"/>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>swap from Diego Tornes</t>
-        </is>
-      </c>
+      <c r="I35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="18" t="n">
@@ -11786,7 +11826,7 @@
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: 1.47</t>
+          <t>Est. R/G: 1.46</t>
         </is>
       </c>
     </row>
@@ -11828,32 +11868,18 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Charlie Meglio</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>0.33</v>
-      </c>
+          <t>-- empty --</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Utility IF</t>
+          <t>(no utility if candidate)</t>
         </is>
       </c>
     </row>
@@ -11939,11 +11965,11 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Anthony Santa Cruz de Oviedo</t>
+          <t>Diego Tornes</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
@@ -11951,16 +11977,16 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.205</v>
+        <v>0.206</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0.286</v>
+        <v>0.308</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>0.082</v>
+        <v>0.102</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>-1.85</v>
+        <v>3.16</v>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
@@ -11976,7 +12002,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Alexander Rincon</t>
+          <t>Anthony Santa Cruz de Oviedo</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
@@ -11988,25 +12014,62 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>Depth</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>Depth</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Alexander Rincon</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n">
         <v>0.202</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="F45" s="4" t="n">
         <v>0.287</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="G45" s="4" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="H44" s="4" t="n">
+      <c r="H45" s="4" t="n">
         <v>1.82</v>
       </c>
-      <c r="I44" s="4" t="inlineStr">
+      <c r="I45" s="4" t="inlineStr">
         <is>
           <t>Depth</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="20" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>Total: 13 players (target 13)</t>
         </is>

--- a/outputs/LAA_roster_system.xlsx
+++ b/outputs/LAA_roster_system.xlsx
@@ -1090,27 +1090,27 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Liam Peterson</t>
+          <t>Walbert Urena</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.369</v>
+        <v>0.334</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.3</v>
+        <v>0.312</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Mid-rotation</t>
+          <t>Back-end starter</t>
         </is>
       </c>
     </row>
@@ -1122,20 +1122,20 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Brody Hopkins</t>
+          <t>Liam Peterson</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.339</v>
+        <v>0.369</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.309</v>
+        <v>0.3</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0</v>
@@ -1154,27 +1154,27 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Victor Mederos</t>
+          <t>Brody Hopkins</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>25</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.354</v>
+        <v>0.339</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.331</v>
+        <v>0.309</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Innings eater</t>
+          <t>Mid-rotation</t>
         </is>
       </c>
     </row>
@@ -1186,23 +1186,23 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Braxton Bragg</t>
+          <t>Victor Mederos</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.356</v>
+        <v>0.354</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.33</v>
+        <v>0.331</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.7</v>
+        <v>-0.8</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -1218,23 +1218,23 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Caden Dana</t>
+          <t>Braxton Bragg</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.364</v>
+        <v>0.356</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.336</v>
+        <v>0.33</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-1.1</v>
+        <v>-0.7</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
@@ -1417,20 +1417,20 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Carlos Espinosa</t>
+          <t>Jose Gonzalez</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
         <v>25</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.38</v>
+        <v>0.373</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.322</v>
+        <v>0.355</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.1</v>
+        <v>-0.8</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>0</v>
@@ -1449,27 +1449,27 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Bridger Holmes</t>
+          <t>Carlos Espinosa</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.382</v>
+        <v>0.38</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.32</v>
+        <v>0.322</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0</v>
+        <v>-0.1</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Mid leverage</t>
+          <t>Low leverage / depth</t>
         </is>
       </c>
     </row>
@@ -1481,27 +1481,27 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Lucas Mahlstedt</t>
+          <t>Bridger Holmes</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
         <v>24</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.384</v>
+        <v>0.382</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.323</v>
+        <v>0.32</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.1</v>
+        <v>-0</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Low leverage / depth</t>
+          <t>Mid leverage</t>
         </is>
       </c>
     </row>
@@ -1605,17 +1605,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Franklin Gomez</t>
+          <t>Caden Dana</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.376</v>
+        <v>0.364</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.335</v>
+        <v>0.336</v>
       </c>
       <c r="F5" s="4" t="n">
         <v>-1.1</v>
@@ -1637,27 +1637,27 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Tyler Bremner</t>
+          <t>Franklin Gomez</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.318</v>
+        <v>0.335</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1</v>
+        <v>-1.1</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Back-end starter</t>
+          <t>Innings eater</t>
         </is>
       </c>
     </row>
@@ -1669,27 +1669,27 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Joel Hurtado</t>
+          <t>Tyler Bremner</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.366</v>
+        <v>0.375</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.328</v>
+        <v>0.318</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.6</v>
+        <v>0.1</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>Innings eater</t>
+          <t>Back-end starter</t>
         </is>
       </c>
     </row>
@@ -1701,27 +1701,27 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Austin Gordon</t>
+          <t>Joel Hurtado</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.383</v>
+        <v>0.366</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.314</v>
+        <v>0.328</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Back-end starter</t>
+          <t>Innings eater</t>
         </is>
       </c>
     </row>
@@ -1733,27 +1733,27 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Jose Gonzalez</t>
+          <t>Austin Gordon</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.373</v>
+        <v>0.383</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.355</v>
+        <v>0.314</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-2.4</v>
+        <v>0.3</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Innings eater</t>
+          <t>Back-end starter</t>
         </is>
       </c>
     </row>
@@ -1868,20 +1868,20 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Samy Natera Jr.</t>
+          <t>Lucas Mahlstedt</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.379</v>
+        <v>0.384</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.372</v>
+        <v>0.323</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.2</v>
+        <v>-0.1</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>0</v>
@@ -1900,20 +1900,20 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Fulton Lockhart</t>
+          <t>Samy Natera Jr.</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.393</v>
+        <v>0.379</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.345</v>
+        <v>0.372</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.6</v>
+        <v>-1.2</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>0</v>
@@ -1932,20 +1932,20 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Yeferson Vargas</t>
+          <t>Fulton Lockhart</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.394</v>
+        <v>0.393</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.354</v>
+        <v>0.345</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.8</v>
+        <v>-0.6</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>0</v>
@@ -1964,17 +1964,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Owen Wild</t>
+          <t>Yeferson Vargas</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.385</v>
+        <v>0.394</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.357</v>
+        <v>0.354</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>-0.8</v>
@@ -1996,20 +1996,20 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Peyton Olejnik</t>
+          <t>Efrain Contreras</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.389</v>
+        <v>0.384</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.35</v>
+        <v>0.383</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.7</v>
+        <v>-1.4</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>0</v>
@@ -2383,20 +2383,20 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Freddy Hernandez</t>
+          <t>Jhon Almonte</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.4</v>
+        <v>0.403</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.374</v>
+        <v>0.357</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.2</v>
+        <v>-0.8</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>0</v>
@@ -2415,17 +2415,17 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Luke Schmolke</t>
+          <t>Owen Wild</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.395</v>
+        <v>0.385</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.354</v>
+        <v>0.357</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>-0.8</v>
@@ -2447,20 +2447,20 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Tate McKee</t>
+          <t>Peyton Olejnik</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.403</v>
+        <v>0.389</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.5</v>
+        <v>-0.7</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>0</v>
@@ -2834,20 +2834,20 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Fabian Soto</t>
+          <t>Freddy Hernandez</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>0.4</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.368</v>
+        <v>0.374</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
@@ -2866,20 +2866,20 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Juan Jordan</t>
+          <t>Luke Schmolke</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.402</v>
+        <v>0.395</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.377</v>
+        <v>0.354</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.3</v>
+        <v>-0.8</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>0</v>
@@ -2898,20 +2898,20 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Cole Raymond</t>
+          <t>Tate McKee</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.401</v>
+        <v>0.403</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.369</v>
+        <v>0.34</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.1</v>
+        <v>-0.5</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>0</v>
@@ -2930,20 +2930,20 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Jhostin Betances</t>
+          <t>Fabian Soto</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>0.4</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.373</v>
+        <v>0.368</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>0</v>
@@ -2962,17 +2962,17 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Sebastian Caseres</t>
+          <t>Juan Jordan</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
         <v>19</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.401</v>
+        <v>0.402</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.381</v>
+        <v>0.377</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>-1.3</v>
@@ -2994,20 +2994,20 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Anllelo Gutierrez</t>
+          <t>Cole Raymond</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.403</v>
+        <v>0.401</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.381</v>
+        <v>0.369</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.3</v>
+        <v>-1.1</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>0</v>
@@ -3026,20 +3026,20 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Barrett Kent</t>
+          <t>Jhostin Betances</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.397</v>
+        <v>0.4</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.365</v>
+        <v>0.373</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1</v>
+        <v>-1.2</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>0</v>
@@ -3317,20 +3317,20 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Wilner Berroteran</t>
+          <t>Sebastian Caseres</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
         <v>19</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.4</v>
+        <v>0.401</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.383</v>
+        <v>0.381</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>0</v>
@@ -3349,17 +3349,17 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Dioris De La Rosa</t>
+          <t>Anllelo Gutierrez</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.4</v>
+        <v>0.403</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.378</v>
+        <v>0.381</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>-1.3</v>
@@ -3381,20 +3381,20 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Fabian Gallardo</t>
+          <t>Barrett Kent</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.4</v>
+        <v>0.397</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.378</v>
+        <v>0.365</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>0</v>
@@ -3413,17 +3413,17 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Anderson Encarnacion</t>
+          <t>Wilner Berroteran</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.402</v>
+        <v>0.4</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.386</v>
+        <v>0.383</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>-1.4</v>
@@ -3445,20 +3445,20 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Jostin Alcantara</t>
+          <t>Fabian Gallardo</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.399</v>
+        <v>0.4</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.394</v>
+        <v>0.378</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.6</v>
+        <v>-1.3</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>0</v>
@@ -3477,20 +3477,20 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Felix Tapia</t>
+          <t>Dioris De La Rosa</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>0.4</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.396</v>
+        <v>0.378</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.7</v>
+        <v>-1.3</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>0</v>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Steuri Amancio</t>
+          <t>Anderson Encarnacion</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
@@ -3519,10 +3519,10 @@
         <v>0.402</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.396</v>
+        <v>0.386</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.7</v>
+        <v>-1.4</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>0</v>
@@ -3539,26 +3539,36 @@
           <t>RP8</t>
         </is>
       </c>
-      <c r="B18" s="29" t="inlineStr">
-        <is>
-          <t>-- empty --</t>
-        </is>
-      </c>
-      <c r="C18" s="30" t="n"/>
-      <c r="D18" s="30" t="n"/>
-      <c r="E18" s="30" t="n"/>
-      <c r="F18" s="30" t="n"/>
-      <c r="G18" s="30" t="n"/>
-      <c r="H18" s="31" t="inlineStr">
-        <is>
-          <t>Sign FA</t>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Jostin Alcantara</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Low leverage / depth</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Total: 12 pitchers (target 13)</t>
+          <t>Total: 13 pitchers (target 13)</t>
         </is>
       </c>
     </row>
@@ -3655,20 +3665,20 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Elias Ledesma</t>
+          <t>Alex Gonzalez</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0.402</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.364</v>
+        <v>0.357</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>-2.9</v>
+        <v>-2.5</v>
       </c>
       <c r="G5" s="4" t="n">
         <v>0</v>
@@ -3687,20 +3697,20 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Alexander Garcia</t>
+          <t>Elias Ledesma</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.4</v>
+        <v>0.402</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.365</v>
+        <v>0.364</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-3</v>
+        <v>-2.9</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>0</v>
@@ -3719,20 +3729,20 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Johnny Slawinski</t>
+          <t>Alexander Garcia</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.399</v>
+        <v>0.4</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.354</v>
+        <v>0.365</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-2.3</v>
+        <v>-3</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>0</v>
@@ -3751,20 +3761,20 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Luke LaCourse</t>
+          <t>Johnny Slawinski</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>20</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.402</v>
+        <v>0.399</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.351</v>
+        <v>0.354</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.1</v>
+        <v>-2.3</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>0</v>
@@ -3783,20 +3793,20 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Jhon Almonte</t>
+          <t>Luke LaCourse</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
         <v>20</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.403</v>
+        <v>0.402</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.357</v>
+        <v>0.351</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-2.5</v>
+        <v>-2.1</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>0</v>
@@ -3820,19 +3830,29 @@
           <t>RP1</t>
         </is>
       </c>
-      <c r="B11" s="29" t="inlineStr">
-        <is>
-          <t>-- empty --</t>
-        </is>
-      </c>
-      <c r="C11" s="30" t="n"/>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="30" t="n"/>
-      <c r="F11" s="30" t="n"/>
-      <c r="G11" s="30" t="n"/>
-      <c r="H11" s="31" t="inlineStr">
-        <is>
-          <t>Sign FA</t>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Felix Tapia</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Low leverage / depth</t>
         </is>
       </c>
     </row>
@@ -3842,19 +3862,29 @@
           <t>RP2</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
-        <is>
-          <t>-- empty --</t>
-        </is>
-      </c>
-      <c r="C12" s="30" t="n"/>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="30" t="n"/>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="30" t="n"/>
-      <c r="H12" s="31" t="inlineStr">
-        <is>
-          <t>Sign FA</t>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Javier Rodriguez</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Low leverage / depth</t>
         </is>
       </c>
     </row>
@@ -3864,19 +3894,29 @@
           <t>RP3</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
-        <is>
-          <t>-- empty --</t>
-        </is>
-      </c>
-      <c r="C13" s="30" t="n"/>
-      <c r="D13" s="30" t="n"/>
-      <c r="E13" s="30" t="n"/>
-      <c r="F13" s="30" t="n"/>
-      <c r="G13" s="30" t="n"/>
-      <c r="H13" s="31" t="inlineStr">
-        <is>
-          <t>Sign FA</t>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Steuri Amancio</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Low leverage / depth</t>
         </is>
       </c>
     </row>
@@ -3886,19 +3926,29 @@
           <t>RP4</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
-        <is>
-          <t>-- empty --</t>
-        </is>
-      </c>
-      <c r="C14" s="30" t="n"/>
-      <c r="D14" s="30" t="n"/>
-      <c r="E14" s="30" t="n"/>
-      <c r="F14" s="30" t="n"/>
-      <c r="G14" s="30" t="n"/>
-      <c r="H14" s="31" t="inlineStr">
-        <is>
-          <t>Sign FA</t>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Steven Cabrera</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0.401</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Low leverage / depth</t>
         </is>
       </c>
     </row>
@@ -3993,7 +4043,7 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Total: 5 pitchers (target 13)</t>
+          <t>Total: 9 pitchers (target 13)</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5670,6 +5720,85 @@
         <v>-1.5</v>
       </c>
       <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Jacob Krieg</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Kauriel Leon</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Brayan Vergara</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="G22" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5779,7 +5908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5868,14 +5997,30 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Rolando Anzola</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Flagged in flagged.txt — rerun once cleared</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Ryan Johnson</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Flagged in flagged.txt — rerun once cleared</t>
         </is>
@@ -14911,27 +15056,27 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Walbert Urena</t>
+          <t>Jack Kochanowicz</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.334</v>
+        <v>0.327</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.312</v>
+        <v>0.325</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.4</v>
+        <v>-0.4</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Back-end starter</t>
+          <t>Innings eater</t>
         </is>
       </c>
     </row>

--- a/outputs/LAA_roster_system.xlsx
+++ b/outputs/LAA_roster_system.xlsx
@@ -1257,27 +1257,27 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Tyler Samaniego</t>
+          <t>Jose Fermin</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.354</v>
+        <v>0.356</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.348</v>
+        <v>0.317</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Low leverage / depth</t>
+          <t>Mid leverage</t>
         </is>
       </c>
     </row>
@@ -1289,23 +1289,23 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Yerry Rodriguez</t>
+          <t>Tyler Samaniego</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.367</v>
+        <v>0.348</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1</v>
+        <v>-0.6</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
@@ -1321,23 +1321,23 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Tyler Owens</t>
+          <t>Yerry Rodriguez</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.362</v>
+        <v>0.353</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.325</v>
+        <v>0.367</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
@@ -1353,20 +1353,20 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Ryan Zeferjahn</t>
+          <t>Tyler Owens</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.359</v>
+        <v>0.362</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.358</v>
+        <v>0.325</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.9</v>
+        <v>-0.1</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>0</v>
@@ -1385,20 +1385,20 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Will Gervase</t>
+          <t>Ryan Zeferjahn</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.366</v>
+        <v>0.359</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.337</v>
+        <v>0.358</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.4</v>
+        <v>-0.9</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>0</v>
@@ -1417,20 +1417,20 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Jose Gonzalez</t>
+          <t>Will Gervase</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.373</v>
+        <v>0.366</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.355</v>
+        <v>0.337</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.8</v>
+        <v>-0.4</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>0</v>
@@ -1449,20 +1449,20 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Carlos Espinosa</t>
+          <t>Jon Olsen</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.38</v>
+        <v>0.369</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.322</v>
+        <v>0.368</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.1</v>
+        <v>-1.1</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>0</v>
@@ -1481,27 +1481,27 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Bridger Holmes</t>
+          <t>Jose Gonzalez</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.382</v>
+        <v>0.373</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.32</v>
+        <v>0.355</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0</v>
+        <v>-0.8</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Mid leverage</t>
+          <t>Low leverage / depth</t>
         </is>
       </c>
     </row>
@@ -1836,20 +1836,20 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Sam Tookoian</t>
+          <t>Carlos Espinosa</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.389</v>
+        <v>0.38</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.346</v>
+        <v>0.322</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>0</v>
@@ -1868,27 +1868,27 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Lucas Mahlstedt</t>
+          <t>Bridger Holmes</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>24</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.384</v>
+        <v>0.382</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.323</v>
+        <v>0.32</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.1</v>
+        <v>-0</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>Low leverage / depth</t>
+          <t>Mid leverage</t>
         </is>
       </c>
     </row>
@@ -1900,20 +1900,20 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Samy Natera Jr.</t>
+          <t>Sam Tookoian</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.379</v>
+        <v>0.389</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.372</v>
+        <v>0.346</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.2</v>
+        <v>-0.6</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>0</v>
@@ -1932,20 +1932,20 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Fulton Lockhart</t>
+          <t>Lucas Mahlstedt</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.393</v>
+        <v>0.384</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.345</v>
+        <v>0.323</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>0</v>
@@ -1964,20 +1964,20 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Yeferson Vargas</t>
+          <t>Samy Natera Jr.</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.394</v>
+        <v>0.379</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.354</v>
+        <v>0.372</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.8</v>
+        <v>-1.2</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>0</v>
@@ -2351,17 +2351,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Ubaldo Soto</t>
+          <t>Fulton Lockhart</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.4</v>
+        <v>0.393</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.347</v>
+        <v>0.345</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>-0.6</v>
@@ -2383,17 +2383,17 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Jhon Almonte</t>
+          <t>Yeferson Vargas</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.403</v>
+        <v>0.394</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.357</v>
+        <v>0.354</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>-0.8</v>
@@ -2802,20 +2802,20 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Drew Lafferty</t>
+          <t>Ubaldo Soto</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.401</v>
+        <v>0.4</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.328</v>
+        <v>0.347</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>0</v>
@@ -2834,20 +2834,20 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Freddy Hernandez</t>
+          <t>Drew Lafferty</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.4</v>
+        <v>0.401</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.374</v>
+        <v>0.328</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.2</v>
+        <v>-0.2</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
@@ -2866,17 +2866,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Luke Schmolke</t>
+          <t>Jhon Almonte</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.395</v>
+        <v>0.403</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.354</v>
+        <v>0.357</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>-0.8</v>
@@ -2898,20 +2898,20 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Tate McKee</t>
+          <t>Freddy Hernandez</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.403</v>
+        <v>0.4</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.34</v>
+        <v>0.374</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.5</v>
+        <v>-1.2</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>0</v>
@@ -2930,20 +2930,20 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Fabian Soto</t>
+          <t>Luke Schmolke</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.4</v>
+        <v>0.395</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.368</v>
+        <v>0.354</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>0</v>
@@ -2962,20 +2962,20 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Juan Jordan</t>
+          <t>Tate McKee</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.402</v>
+        <v>0.403</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.377</v>
+        <v>0.34</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.3</v>
+        <v>-0.5</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>0</v>
@@ -2994,17 +2994,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Cole Raymond</t>
+          <t>Fabian Soto</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.401</v>
+        <v>0.4</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.369</v>
+        <v>0.368</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>-1.1</v>
@@ -3026,20 +3026,20 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Jhostin Betances</t>
+          <t>Juan Jordan</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.4</v>
+        <v>0.402</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.373</v>
+        <v>0.377</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.2</v>
+        <v>-1.3</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>0</v>
@@ -3317,20 +3317,20 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Sebastian Caseres</t>
+          <t>Cole Raymond</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>0.401</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.381</v>
+        <v>0.369</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.3</v>
+        <v>-1.1</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>0</v>
@@ -3349,17 +3349,17 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Anllelo Gutierrez</t>
+          <t>Ricky Mora</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
         <v>17</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.403</v>
+        <v>0.402</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.381</v>
+        <v>0.379</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>-1.3</v>
@@ -3381,20 +3381,20 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Barrett Kent</t>
+          <t>Jhostin Betances</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.397</v>
+        <v>0.4</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.365</v>
+        <v>0.373</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1</v>
+        <v>-1.2</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>0</v>
@@ -3413,20 +3413,20 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Wilner Berroteran</t>
+          <t>Sebastian Caseres</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>19</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.4</v>
+        <v>0.401</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.383</v>
+        <v>0.381</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>0</v>
@@ -3445,17 +3445,17 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Fabian Gallardo</t>
+          <t>Anllelo Gutierrez</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.4</v>
+        <v>0.403</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.378</v>
+        <v>0.381</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>-1.3</v>
@@ -3477,20 +3477,20 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Dioris De La Rosa</t>
+          <t>Barrett Kent</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.4</v>
+        <v>0.397</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.378</v>
+        <v>0.365</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>0</v>
@@ -3509,17 +3509,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Anderson Encarnacion</t>
+          <t>Wilner Berroteran</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.402</v>
+        <v>0.4</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.386</v>
+        <v>0.383</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>-1.4</v>
@@ -3541,20 +3541,20 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Jostin Alcantara</t>
+          <t>Fabian Gallardo</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.399</v>
+        <v>0.4</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.394</v>
+        <v>0.378</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.6</v>
+        <v>-1.3</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>0</v>
@@ -3832,20 +3832,20 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Felix Tapia</t>
+          <t>Dioris De La Rosa</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>0.4</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.396</v>
+        <v>0.378</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-1.7</v>
+        <v>-1.3</v>
       </c>
       <c r="G11" s="4" t="n">
         <v>0</v>
@@ -3864,20 +3864,20 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Javier Rodriguez</t>
+          <t>Anderson Encarnacion</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>0.402</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.396</v>
+        <v>0.386</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.7</v>
+        <v>-1.4</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>0</v>
@@ -3896,20 +3896,20 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Steuri Amancio</t>
+          <t>Frank Favila</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>0.402</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.396</v>
+        <v>0.393</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>0</v>
@@ -3928,20 +3928,20 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Steven Cabrera</t>
+          <t>Jostin Alcantara</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.401</v>
+        <v>0.399</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.396</v>
+        <v>0.394</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>0</v>
@@ -3958,19 +3958,29 @@
           <t>RP5</t>
         </is>
       </c>
-      <c r="B15" s="29" t="inlineStr">
-        <is>
-          <t>-- empty --</t>
-        </is>
-      </c>
-      <c r="C15" s="30" t="n"/>
-      <c r="D15" s="30" t="n"/>
-      <c r="E15" s="30" t="n"/>
-      <c r="F15" s="30" t="n"/>
-      <c r="G15" s="30" t="n"/>
-      <c r="H15" s="31" t="inlineStr">
-        <is>
-          <t>Sign FA</t>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Felix Tapia</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Low leverage / depth</t>
         </is>
       </c>
     </row>
@@ -3980,19 +3990,29 @@
           <t>RP6</t>
         </is>
       </c>
-      <c r="B16" s="29" t="inlineStr">
-        <is>
-          <t>-- empty --</t>
-        </is>
-      </c>
-      <c r="C16" s="30" t="n"/>
-      <c r="D16" s="30" t="n"/>
-      <c r="E16" s="30" t="n"/>
-      <c r="F16" s="30" t="n"/>
-      <c r="G16" s="30" t="n"/>
-      <c r="H16" s="31" t="inlineStr">
-        <is>
-          <t>Sign FA</t>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Javier Rodriguez</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Low leverage / depth</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4063,7 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Total: 9 pitchers (target 13)</t>
+          <t>Total: 11 pitchers (target 13)</t>
         </is>
       </c>
     </row>
@@ -5245,7 +5265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5645,11 +5665,11 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Andres Cova</t>
+          <t>Davidxon Lara</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
@@ -5659,9 +5679,7 @@
       <c r="D17" s="4" t="n">
         <v>0.4</v>
       </c>
-      <c r="E17" s="4" t="n">
-        <v>-3.5</v>
-      </c>
+      <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="n">
         <v>-1.2</v>
       </c>
@@ -5672,7 +5690,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Marco Vega</t>
+          <t>Andres Cova</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
@@ -5687,10 +5705,10 @@
         <v>0.4</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.2</v>
+        <v>-3.5</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.4</v>
+        <v>-1.2</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>0</v>
@@ -5699,25 +5717,25 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Nick Parker</t>
+          <t>Marco Vega</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-4.6</v>
+        <v>-4.2</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.5</v>
+        <v>-1.4</v>
       </c>
       <c r="G19" s="4" t="n">
         <v>0</v>
@@ -5726,25 +5744,25 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Jacob Krieg</t>
+          <t>Nick Parker</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-5.3</v>
+        <v>-4.6</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.8</v>
+        <v>-1.5</v>
       </c>
       <c r="G20" s="4" t="n">
         <v>0</v>
@@ -5753,11 +5771,11 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Kauriel Leon</t>
+          <t>Victor De La Cruz</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
@@ -5768,10 +5786,10 @@
         <v>0.402</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-5.4</v>
+        <v>-5.1</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.8</v>
+        <v>-1.7</v>
       </c>
       <c r="G21" s="4" t="n">
         <v>0</v>
@@ -5780,11 +5798,11 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Brayan Vergara</t>
+          <t>Steven Cabrera</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
@@ -5792,13 +5810,117 @@
         </is>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.4</v>
+        <v>0.401</v>
       </c>
       <c r="E22" s="4" t="inlineStr"/>
       <c r="F22" s="4" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Steuri Amancio</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Starling Reyes</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="n">
         <v>-1.8</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G24" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Kauriel Leon</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Brayan Vergara</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="G26" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15287,20 +15409,20 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Chase Silseth</t>
+          <t>Brady Choban</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
         <v>26</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.349</v>
+        <v>0.347</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.35</v>
+        <v>0.346</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.7</v>
+        <v>-0.6</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>0</v>
@@ -15319,27 +15441,27 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Jose Fermin</t>
+          <t>Chase Silseth</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.356</v>
+        <v>0.349</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.317</v>
+        <v>0.35</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Mid leverage</t>
+          <t>Low leverage / depth</t>
         </is>
       </c>
     </row>

--- a/outputs/LAA_roster_system.xlsx
+++ b/outputs/LAA_roster_system.xlsx
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.92</v>
+        <v>-4.13</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.52</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="9">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-5.53</v>
+        <v>-5.35</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.57</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="10">
@@ -12387,11 +12387,11 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Alexander Rincon</t>
+          <t>Samil Dishmey</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
@@ -12399,16 +12399,16 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.202</v>
+        <v>0.207</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>0.287</v>
+        <v>0.263</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.056</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>1.82</v>
+        <v>-2.72</v>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
@@ -12798,11 +12798,11 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Samil Dishmey</t>
+          <t>Alexander Rincon</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
@@ -12810,16 +12810,16 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.207</v>
+        <v>0.202</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.263</v>
+        <v>0.287</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.056</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-2.72</v>
+        <v>1.82</v>
       </c>
       <c r="I13" s="4" t="inlineStr"/>
     </row>
@@ -13128,20 +13128,20 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Samil Dishmey</t>
+          <t>Alexander Rincon</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.196</v>
+        <v>0.212</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.207</v>
+        <v>0.202</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.011</v>
+        <v>0.01</v>
       </c>
       <c r="H24" s="4" t="n"/>
       <c r="I24" s="4" t="n"/>
@@ -13149,7 +13149,7 @@
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: 0.23</t>
+          <t>Est. R/G: 0.29</t>
         </is>
       </c>
     </row>
@@ -13205,7 +13205,7 @@
     </row>
     <row r="28">
       <c r="A28" s="18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
     </row>
     <row r="29">
       <c r="A29" s="18" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B29" s="18" t="inlineStr">
         <is>
@@ -13243,31 +13243,27 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Samil Dishmey</t>
+          <t>Sandy Ruiz</t>
         </is>
       </c>
       <c r="D29" s="4" t="n">
         <v>21</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.234</v>
+        <v>0.185</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.207</v>
+        <v>0.185</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>swap from Sandy Ruiz</t>
-        </is>
-      </c>
+      <c r="I29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
@@ -13296,7 +13292,7 @@
     </row>
     <row r="31">
       <c r="A31" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B31" s="18" t="inlineStr">
         <is>
@@ -13325,7 +13321,7 @@
     </row>
     <row r="32">
       <c r="A32" s="18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
@@ -13354,7 +13350,7 @@
     </row>
     <row r="33">
       <c r="A33" s="18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B33" s="18" t="inlineStr">
         <is>
@@ -13383,7 +13379,7 @@
     </row>
     <row r="34">
       <c r="A34" s="18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
@@ -13412,7 +13408,7 @@
     </row>
     <row r="35">
       <c r="A35" s="18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B35" s="18" t="inlineStr">
         <is>
@@ -13441,7 +13437,7 @@
     </row>
     <row r="36">
       <c r="A36" s="18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
@@ -13468,14 +13464,14 @@
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>swap from Samil Dishmey</t>
+          <t>swap from Alexander Rincon</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>Est. R/G: 0.66</t>
+          <t>Est. R/G: 0.47</t>
         </is>
       </c>
     </row>
